--- a/144/DQ Templates and Instructions/Topic 5 DQ 2/Topic 5 DQ 2.xlsx
+++ b/144/DQ Templates and Instructions/Topic 5 DQ 2/Topic 5 DQ 2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gcumail.sharepoint.com/sites/MathematicsProgramFacultyStaff-MATOFTF/Shared Documents/MATOFTF/ALEKS/DQ Templates and Instructions/Topic 5 DQ 2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="202" documentId="13_ncr:1_{01544684-905C-417E-A831-5CA460CC2737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7017FD07-A264-4624-A7AA-35CB23E3535A}"/>
+  <xr:revisionPtr revIDLastSave="254" documentId="13_ncr:1_{01544684-905C-417E-A831-5CA460CC2737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{73A50AFA-4D2F-4B57-9190-72834D101F81}"/>
   <bookViews>
-    <workbookView xWindow="1800" yWindow="2085" windowWidth="27000" windowHeight="14115" tabRatio="649" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="649" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Goals and Instructions" sheetId="7" r:id="rId1"/>
@@ -47,6 +47,42 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={B05C9DDC-E061-4B91-8296-E0F41DA1E339}</author>
+    <author>tc={4DED145D-9386-4D2F-86D3-6933C31D540A}</author>
+    <author>tc={7D93A252-A397-45CF-87F5-D3804D5EAFA7}</author>
+  </authors>
+  <commentList>
+    <comment ref="F2" authorId="0" shapeId="0" xr:uid="{B05C9DDC-E061-4B91-8296-E0F41DA1E339}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    https://www.loom.com/share/d75e2dbd00674adc8cc09d59d90c3a7d?sid=50a5c7ae-f145-4875-bf35-04ec7babbbb8</t>
+      </text>
+    </comment>
+    <comment ref="F3" authorId="1" shapeId="0" xr:uid="{4DED145D-9386-4D2F-86D3-6933C31D540A}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    https://www.loom.com/share/4e999e54029a43d8b7b58d21e26817f7?sid=a1a57bba-9bd0-4ab2-994a-0c2b2c65ef01</t>
+      </text>
+    </comment>
+    <comment ref="F4" authorId="2" shapeId="0" xr:uid="{7D93A252-A397-45CF-87F5-D3804D5EAFA7}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    https://www.loom.com/share/2c7609c4acb140e0b9aa4a95e0ae0440</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="494">
   <si>
@@ -1601,7 +1637,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1726,6 +1762,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="8">
@@ -2182,92 +2224,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2310,38 +2280,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="7" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -2368,42 +2306,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2449,93 +2351,219 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="7" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
-      <protection locked="0"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
-      <protection locked="0"/>
+      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
-      <protection locked="0"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
+      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
+      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
+      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
+      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
+      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
+      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
+      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
+      <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2559,6 +2587,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Richard Ketchersid" id="{7D363727-7BC8-4A19-85A9-62EDC04791BF}" userId="S::richard.ketchersid@gcu.edu::a14ec2f7-27bd-40c3-90d9-209834cdef57" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2822,6 +2856,38 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="F2" dT="2026-07-16T19:58:59.69" personId="{7D363727-7BC8-4A19-85A9-62EDC04791BF}" id="{B05C9DDC-E061-4B91-8296-E0F41DA1E339}">
+    <text>https://www.loom.com/share/d75e2dbd00674adc8cc09d59d90c3a7d?sid=50a5c7ae-f145-4875-bf35-04ec7babbbb8</text>
+    <extLst>
+      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
+        <xltc2:checksum>923284797</xltc2:checksum>
+        <xltc2:hyperlink startIndex="0" length="100" url="https://www.loom.com/share/d75e2dbd00674adc8cc09d59d90c3a7d?sid=50a5c7ae-f145-4875-bf35-04ec7babbbb8"/>
+      </x:ext>
+    </extLst>
+  </threadedComment>
+  <threadedComment ref="F3" dT="2026-07-16T19:59:17.40" personId="{7D363727-7BC8-4A19-85A9-62EDC04791BF}" id="{4DED145D-9386-4D2F-86D3-6933C31D540A}">
+    <text>https://www.loom.com/share/4e999e54029a43d8b7b58d21e26817f7?sid=a1a57bba-9bd0-4ab2-994a-0c2b2c65ef01</text>
+    <extLst>
+      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
+        <xltc2:checksum>4210359309</xltc2:checksum>
+        <xltc2:hyperlink startIndex="0" length="100" url="https://www.loom.com/share/4e999e54029a43d8b7b58d21e26817f7?sid=a1a57bba-9bd0-4ab2-994a-0c2b2c65ef01"/>
+      </x:ext>
+    </extLst>
+  </threadedComment>
+  <threadedComment ref="F4" dT="2026-07-16T19:59:39.06" personId="{7D363727-7BC8-4A19-85A9-62EDC04791BF}" id="{7D93A252-A397-45CF-87F5-D3804D5EAFA7}">
+    <text>https://www.loom.com/share/2c7609c4acb140e0b9aa4a95e0ae0440</text>
+    <extLst>
+      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
+        <xltc2:checksum>2001432892</xltc2:checksum>
+        <xltc2:hyperlink startIndex="0" length="59" url="https://www.loom.com/share/2c7609c4acb140e0b9aa4a95e0ae0440"/>
+      </x:ext>
+    </extLst>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B26E836-EB4A-468C-A998-F38E02B7A9E0}">
   <dimension ref="B2:I13"/>
@@ -2832,83 +2898,83 @@
   <sheetData>
     <row r="2" spans="2:9" ht="15.75" thickBot="1"/>
     <row r="3" spans="2:9" ht="15.75" thickBot="1">
-      <c r="B3" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="48"/>
+      <c r="B3" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="20"/>
     </row>
     <row r="4" spans="2:9">
       <c r="B4" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="49"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="51"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="23"/>
     </row>
     <row r="5" spans="2:9" ht="30">
-      <c r="B5" s="37" t="s">
+      <c r="B5" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="49"/>
-      <c r="E5" s="50"/>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50"/>
-      <c r="H5" s="50"/>
-      <c r="I5" s="51"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="22"/>
+      <c r="I5" s="23"/>
     </row>
     <row r="6" spans="2:9" ht="30">
-      <c r="B6" s="37" t="s">
+      <c r="B6" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="49"/>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50"/>
-      <c r="H6" s="50"/>
-      <c r="I6" s="51"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="23"/>
     </row>
     <row r="7" spans="2:9" ht="15.75" thickBot="1">
-      <c r="B7" s="37"/>
-      <c r="D7" s="52"/>
-      <c r="E7" s="53"/>
-      <c r="F7" s="53"/>
-      <c r="G7" s="53"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="54"/>
+      <c r="B7" s="17"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="25"/>
+      <c r="I7" s="26"/>
     </row>
     <row r="8" spans="2:9">
-      <c r="B8" s="36"/>
+      <c r="B8" s="16"/>
     </row>
     <row r="9" spans="2:9" ht="15.75" thickBot="1">
-      <c r="B9" s="36"/>
+      <c r="B9" s="16"/>
     </row>
     <row r="10" spans="2:9" ht="15.75" thickBot="1">
-      <c r="B10" s="35" t="s">
+      <c r="B10" s="15" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="11" spans="2:9">
-      <c r="B11" s="36" t="s">
+      <c r="B11" s="16" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="12" spans="2:9">
-      <c r="B12" s="37" t="s">
+      <c r="B12" s="17" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="13" spans="2:9">
-      <c r="B13" s="36" t="s">
+      <c r="B13" s="16" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2921,15 +2987,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:AK103"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="8"/>
-    <col min="2" max="2" width="11.85546875" style="8" customWidth="1"/>
-    <col min="3" max="3" width="9" customWidth="1"/>
-    <col min="4" max="4" width="19.28515625" style="4" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="6"/>
+    <col min="2" max="2" width="11.85546875" style="6" customWidth="1"/>
+    <col min="3" max="3" width="9" style="4" customWidth="1"/>
+    <col min="4" max="4" width="20.140625" style="4" customWidth="1"/>
     <col min="5" max="5" width="19.42578125" style="4" customWidth="1"/>
     <col min="6" max="6" width="11.28515625" style="4" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.42578125" style="4" bestFit="1" customWidth="1"/>
@@ -2939,1781 +3005,1780 @@
     <col min="11" max="11" width="22.28515625" style="4" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="23.42578125" style="4" bestFit="1" customWidth="1"/>
     <col min="13" max="36" width="9.140625" style="4"/>
-    <col min="37" max="37" width="12.85546875" style="7" hidden="1" customWidth="1"/>
+    <col min="37" max="37" width="12.85546875" style="4" hidden="1" customWidth="1"/>
     <col min="38" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="43.9" customHeight="1" thickBot="1">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="AK1" s="6"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
     </row>
     <row r="2" spans="1:37" ht="20.25" thickTop="1" thickBot="1">
-      <c r="A2" s="8">
-        <v>1</v>
-      </c>
-      <c r="B2" s="13" t="str">
+      <c r="A2" s="6">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D12,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D2" s="38" t="s">
+      <c r="D2" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="9"/>
-      <c r="F2" s="87" t="s">
+      <c r="E2" s="52"/>
+      <c r="F2" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="88"/>
-      <c r="H2" s="89"/>
-      <c r="J2" s="64" t="s">
+      <c r="G2" s="54"/>
+      <c r="H2" s="55"/>
+      <c r="J2" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="65"/>
-      <c r="AK2" s="6">
+      <c r="K2" s="28"/>
+      <c r="AK2" s="4">
         <f>MOD(CODE(MID(D2,1,1))*CODE(MID(D2,2,1))*CODE(MID(D2,3,1))*1103515245 + 12345,9172)</f>
         <v>5008</v>
       </c>
     </row>
     <row r="3" spans="1:37" ht="19.5" thickBot="1">
-      <c r="A3" s="8">
+      <c r="A3" s="6">
         <f>A2+1</f>
         <v>2</v>
       </c>
-      <c r="B3" s="13" t="str">
+      <c r="B3" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D13,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="E3" s="9"/>
-      <c r="F3" s="90" t="s">
+      <c r="E3" s="52"/>
+      <c r="F3" s="53" t="s">
         <v>491</v>
       </c>
-      <c r="G3" s="91"/>
-      <c r="H3" s="92"/>
-      <c r="J3" s="27" t="s">
+      <c r="G3" s="54"/>
+      <c r="H3" s="55"/>
+      <c r="J3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="K3" s="28" t="s">
+      <c r="K3" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="AK3" s="6">
+      <c r="AK3" s="4">
         <f>MOD(AK2*1103515245 + 12345,9172)</f>
         <v>6441</v>
       </c>
     </row>
     <row r="4" spans="1:37" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A4" s="8">
+      <c r="A4" s="6">
         <f t="shared" ref="A4:A67" si="0">A3+1</f>
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="str">
+      <c r="B4" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D14,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="56" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="14"/>
-      <c r="F4" s="90" t="s">
+      <c r="E4" s="57"/>
+      <c r="F4" s="53" t="s">
         <v>493</v>
       </c>
-      <c r="G4" s="91"/>
-      <c r="H4" s="92"/>
-      <c r="J4" s="29" t="s">
+      <c r="G4" s="54"/>
+      <c r="H4" s="55"/>
+      <c r="J4" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="K4" s="30" t="s">
+      <c r="K4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="AK4" s="6">
+      <c r="AK4" s="4">
         <f t="shared" ref="AK4:AK67" si="1">MOD(AK3*1103515245 + 12345,9172)</f>
         <v>5030</v>
       </c>
     </row>
     <row r="5" spans="1:37" ht="16.5" customHeight="1" thickBot="1">
-      <c r="A5" s="8">
+      <c r="A5" s="6">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B5" s="13" t="str">
+      <c r="B5" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D15,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="58" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="19"/>
-      <c r="G5" s="43"/>
-      <c r="H5" s="44"/>
-      <c r="J5" s="31" t="s">
+      <c r="E5" s="44"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="60"/>
+      <c r="J5" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="K5" s="30" t="s">
+      <c r="K5" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="AK5" s="6">
+      <c r="AK5" s="4">
         <f t="shared" si="1"/>
         <v>2547</v>
       </c>
     </row>
     <row r="6" spans="1:37" ht="15.75">
-      <c r="A6" s="8">
+      <c r="A6" s="6">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B6" s="13" t="str">
+      <c r="B6" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D16,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="61" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="20"/>
-      <c r="G6" s="93" t="s">
+      <c r="E6" s="45"/>
+      <c r="G6" s="62" t="s">
         <v>492</v>
       </c>
-      <c r="H6" s="94"/>
-      <c r="J6" s="32" t="s">
+      <c r="H6" s="63"/>
+      <c r="J6" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="K6" s="30" t="s">
+      <c r="K6" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="AK6" s="6">
+      <c r="AK6" s="4">
         <f t="shared" si="1"/>
         <v>6368</v>
       </c>
     </row>
     <row r="7" spans="1:37" ht="16.5" thickBot="1">
-      <c r="A7" s="8">
+      <c r="A7" s="6">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B7" s="13" t="str">
+      <c r="B7" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D17,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="64" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="39"/>
-      <c r="G7" s="95"/>
-      <c r="H7" s="96"/>
-      <c r="J7" s="33" t="s">
+      <c r="E7" s="46"/>
+      <c r="G7" s="65"/>
+      <c r="H7" s="66"/>
+      <c r="J7" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="K7" s="34" t="s">
+      <c r="K7" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="AK7" s="6">
+      <c r="AK7" s="4">
         <f t="shared" si="1"/>
         <v>4193</v>
       </c>
     </row>
     <row r="8" spans="1:37" ht="15.75" thickBot="1">
-      <c r="A8" s="8">
+      <c r="A8" s="6">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B8" s="13" t="str">
+      <c r="B8" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D18,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK8" s="6">
+      <c r="AK8" s="4">
         <f>MOD(AK7*1103515245 + 12345,9172)</f>
         <v>8530</v>
       </c>
     </row>
     <row r="9" spans="1:37" ht="15.75" thickBot="1">
-      <c r="A9" s="8">
+      <c r="A9" s="6">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B9" s="13" t="str">
+      <c r="B9" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D19,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D9" s="75" t="s">
+      <c r="D9" s="67" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="76"/>
-      <c r="F9" s="76"/>
-      <c r="G9" s="76"/>
-      <c r="H9" s="77"/>
-      <c r="AK9" s="6">
+      <c r="E9" s="68"/>
+      <c r="F9" s="68"/>
+      <c r="G9" s="68"/>
+      <c r="H9" s="69"/>
+      <c r="AK9" s="4">
         <f t="shared" si="1"/>
         <v>6743</v>
       </c>
     </row>
     <row r="10" spans="1:37" ht="15" customHeight="1" thickBot="1">
-      <c r="A10" s="8">
+      <c r="A10" s="6">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B10" s="13" t="str">
+      <c r="B10" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D20,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D10" s="23" t="s">
+      <c r="D10" s="70" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="24" t="s">
+      <c r="E10" s="71" t="s">
         <v>31</v>
       </c>
-      <c r="F10" s="24" t="s">
+      <c r="F10" s="71" t="s">
         <v>32</v>
       </c>
-      <c r="G10" s="24" t="s">
+      <c r="G10" s="71" t="s">
         <v>33</v>
       </c>
-      <c r="H10" s="25" t="s">
+      <c r="H10" s="72" t="s">
         <v>34</v>
       </c>
-      <c r="J10" s="78" t="s">
+      <c r="J10" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="K10" s="79"/>
-      <c r="L10" s="79"/>
-      <c r="M10" s="79"/>
-      <c r="N10" s="79"/>
-      <c r="O10" s="80"/>
-      <c r="AK10" s="6">
+      <c r="K10" s="74"/>
+      <c r="L10" s="74"/>
+      <c r="M10" s="74"/>
+      <c r="N10" s="74"/>
+      <c r="O10" s="75"/>
+      <c r="AK10" s="4">
         <f t="shared" si="1"/>
         <v>6608</v>
       </c>
     </row>
     <row r="11" spans="1:37" ht="15.75">
-      <c r="A11" s="8">
+      <c r="A11" s="6">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B11" s="13" t="str">
+      <c r="B11" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D21,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D11" s="21"/>
-      <c r="E11" s="40"/>
-      <c r="F11" s="40"/>
-      <c r="G11" s="22"/>
-      <c r="H11" s="42"/>
-      <c r="J11" s="81"/>
-      <c r="K11" s="82"/>
-      <c r="L11" s="82"/>
-      <c r="M11" s="82"/>
-      <c r="N11" s="82"/>
-      <c r="O11" s="83"/>
-      <c r="AK11" s="6">
+      <c r="D11" s="40"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="42"/>
+      <c r="H11" s="47"/>
+      <c r="J11" s="76"/>
+      <c r="K11" s="77"/>
+      <c r="L11" s="77"/>
+      <c r="M11" s="77"/>
+      <c r="N11" s="77"/>
+      <c r="O11" s="78"/>
+      <c r="AK11" s="4">
         <f t="shared" si="1"/>
         <v>7573</v>
       </c>
     </row>
     <row r="12" spans="1:37" ht="15.75">
-      <c r="A12" s="8">
+      <c r="A12" s="6">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B12" s="13" t="str">
+      <c r="B12" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D22,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D12" s="41"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="40"/>
-      <c r="G12" s="22"/>
-      <c r="H12" s="42"/>
-      <c r="J12" s="81"/>
-      <c r="K12" s="82"/>
-      <c r="L12" s="82"/>
-      <c r="M12" s="82"/>
-      <c r="N12" s="82"/>
-      <c r="O12" s="83"/>
-      <c r="AK12" s="6">
+      <c r="D12" s="43"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="47"/>
+      <c r="J12" s="76"/>
+      <c r="K12" s="77"/>
+      <c r="L12" s="77"/>
+      <c r="M12" s="77"/>
+      <c r="N12" s="77"/>
+      <c r="O12" s="78"/>
+      <c r="AK12" s="4">
         <f t="shared" si="1"/>
         <v>6450</v>
       </c>
     </row>
     <row r="13" spans="1:37" ht="15.75">
-      <c r="A13" s="8">
+      <c r="A13" s="6">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B13" s="13" t="str">
+      <c r="B13" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D23,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D13" s="41"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="40"/>
-      <c r="G13" s="22"/>
-      <c r="H13" s="42"/>
-      <c r="J13" s="81"/>
-      <c r="K13" s="82"/>
-      <c r="L13" s="82"/>
-      <c r="M13" s="82"/>
-      <c r="N13" s="82"/>
-      <c r="O13" s="83"/>
-      <c r="AK13" s="6">
+      <c r="D13" s="43"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="47"/>
+      <c r="J13" s="76"/>
+      <c r="K13" s="77"/>
+      <c r="L13" s="77"/>
+      <c r="M13" s="77"/>
+      <c r="N13" s="77"/>
+      <c r="O13" s="78"/>
+      <c r="AK13" s="4">
         <f t="shared" si="1"/>
         <v>8023</v>
       </c>
     </row>
     <row r="14" spans="1:37" ht="15.75">
-      <c r="A14" s="8">
+      <c r="A14" s="6">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B14" s="13" t="str">
+      <c r="B14" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D24,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D14" s="41"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="40"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="42"/>
-      <c r="J14" s="81"/>
-      <c r="K14" s="82"/>
-      <c r="L14" s="82"/>
-      <c r="M14" s="82"/>
-      <c r="N14" s="82"/>
-      <c r="O14" s="83"/>
-      <c r="AK14" s="6">
+      <c r="D14" s="43"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="47"/>
+      <c r="J14" s="76"/>
+      <c r="K14" s="77"/>
+      <c r="L14" s="77"/>
+      <c r="M14" s="77"/>
+      <c r="N14" s="77"/>
+      <c r="O14" s="78"/>
+      <c r="AK14" s="4">
         <f>MOD(AK13*1103515245 + 12345,9172)</f>
         <v>176</v>
       </c>
     </row>
     <row r="15" spans="1:37" ht="15.75">
-      <c r="A15" s="8">
+      <c r="A15" s="6">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B15" s="13" t="str">
+      <c r="B15" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D25,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D15" s="41"/>
-      <c r="E15" s="40"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="42"/>
-      <c r="J15" s="81"/>
-      <c r="K15" s="82"/>
-      <c r="L15" s="82"/>
-      <c r="M15" s="82"/>
-      <c r="N15" s="82"/>
-      <c r="O15" s="83"/>
-      <c r="AK15" s="6">
+      <c r="D15" s="43"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="42"/>
+      <c r="H15" s="47"/>
+      <c r="J15" s="76"/>
+      <c r="K15" s="77"/>
+      <c r="L15" s="77"/>
+      <c r="M15" s="77"/>
+      <c r="N15" s="77"/>
+      <c r="O15" s="78"/>
+      <c r="AK15" s="4">
         <f t="shared" si="1"/>
         <v>8709</v>
       </c>
     </row>
     <row r="16" spans="1:37" ht="15.75" customHeight="1">
-      <c r="A16" s="8">
+      <c r="A16" s="6">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B16" s="13" t="str">
+      <c r="B16" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D26,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D16" s="41"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="40"/>
-      <c r="G16" s="22"/>
-      <c r="H16" s="42"/>
-      <c r="J16" s="81"/>
-      <c r="K16" s="82"/>
-      <c r="L16" s="82"/>
-      <c r="M16" s="82"/>
-      <c r="N16" s="82"/>
-      <c r="O16" s="83"/>
-      <c r="AK16" s="6">
+      <c r="D16" s="43"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="42"/>
+      <c r="H16" s="47"/>
+      <c r="J16" s="76"/>
+      <c r="K16" s="77"/>
+      <c r="L16" s="77"/>
+      <c r="M16" s="77"/>
+      <c r="N16" s="77"/>
+      <c r="O16" s="78"/>
+      <c r="AK16" s="4">
         <f t="shared" si="1"/>
         <v>7162</v>
       </c>
     </row>
     <row r="17" spans="1:37" ht="15.75">
-      <c r="A17" s="8">
+      <c r="A17" s="6">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B17" s="13" t="str">
+      <c r="B17" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D27,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D17" s="41"/>
-      <c r="E17" s="40"/>
-      <c r="F17" s="40"/>
-      <c r="G17" s="22"/>
-      <c r="H17" s="42"/>
-      <c r="J17" s="81"/>
-      <c r="K17" s="82"/>
-      <c r="L17" s="82"/>
-      <c r="M17" s="82"/>
-      <c r="N17" s="82"/>
-      <c r="O17" s="83"/>
-      <c r="AK17" s="6">
+      <c r="D17" s="43"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="42"/>
+      <c r="H17" s="47"/>
+      <c r="J17" s="76"/>
+      <c r="K17" s="77"/>
+      <c r="L17" s="77"/>
+      <c r="M17" s="77"/>
+      <c r="N17" s="77"/>
+      <c r="O17" s="78"/>
+      <c r="AK17" s="4">
         <f t="shared" si="1"/>
         <v>1235</v>
       </c>
     </row>
     <row r="18" spans="1:37" ht="15.75">
-      <c r="A18" s="8">
+      <c r="A18" s="6">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B18" s="13" t="str">
+      <c r="B18" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D28,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D18" s="41"/>
-      <c r="E18" s="40"/>
-      <c r="F18" s="40"/>
-      <c r="G18" s="22"/>
-      <c r="H18" s="42"/>
-      <c r="J18" s="81"/>
-      <c r="K18" s="82"/>
-      <c r="L18" s="82"/>
-      <c r="M18" s="82"/>
-      <c r="N18" s="82"/>
-      <c r="O18" s="83"/>
-      <c r="AK18" s="6">
+      <c r="D18" s="43"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="47"/>
+      <c r="J18" s="76"/>
+      <c r="K18" s="77"/>
+      <c r="L18" s="77"/>
+      <c r="M18" s="77"/>
+      <c r="N18" s="77"/>
+      <c r="O18" s="78"/>
+      <c r="AK18" s="4">
         <f t="shared" si="1"/>
         <v>120</v>
       </c>
     </row>
     <row r="19" spans="1:37" ht="15" customHeight="1">
-      <c r="A19" s="8">
+      <c r="A19" s="6">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B19" s="13" t="str">
+      <c r="B19" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D29,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D19" s="41"/>
-      <c r="E19" s="40"/>
-      <c r="F19" s="40"/>
-      <c r="G19" s="22"/>
-      <c r="H19" s="42"/>
-      <c r="J19" s="81"/>
-      <c r="K19" s="82"/>
-      <c r="L19" s="82"/>
-      <c r="M19" s="82"/>
-      <c r="N19" s="82"/>
-      <c r="O19" s="83"/>
-      <c r="Q19" s="5"/>
-      <c r="AK19" s="6">
+      <c r="D19" s="43"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="47"/>
+      <c r="J19" s="76"/>
+      <c r="K19" s="77"/>
+      <c r="L19" s="77"/>
+      <c r="M19" s="77"/>
+      <c r="N19" s="77"/>
+      <c r="O19" s="78"/>
+      <c r="Q19" s="79"/>
+      <c r="AK19" s="4">
         <f t="shared" si="1"/>
         <v>277</v>
       </c>
     </row>
     <row r="20" spans="1:37" ht="15.75">
-      <c r="A20" s="8">
+      <c r="A20" s="6">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B20" s="13" t="str">
+      <c r="B20" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D30,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D20" s="41"/>
-      <c r="E20" s="40"/>
-      <c r="F20" s="40"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="42"/>
-      <c r="J20" s="81"/>
-      <c r="K20" s="82"/>
-      <c r="L20" s="82"/>
-      <c r="M20" s="82"/>
-      <c r="N20" s="82"/>
-      <c r="O20" s="83"/>
-      <c r="Q20" s="5"/>
-      <c r="AK20" s="6">
+      <c r="D20" s="43"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="47"/>
+      <c r="J20" s="76"/>
+      <c r="K20" s="77"/>
+      <c r="L20" s="77"/>
+      <c r="M20" s="77"/>
+      <c r="N20" s="77"/>
+      <c r="O20" s="78"/>
+      <c r="Q20" s="79"/>
+      <c r="AK20" s="4">
         <f t="shared" si="1"/>
         <v>4590</v>
       </c>
     </row>
     <row r="21" spans="1:37" ht="15.75">
-      <c r="A21" s="8">
+      <c r="A21" s="6">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B21" s="13" t="str">
+      <c r="B21" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D31,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D21" s="41"/>
-      <c r="E21" s="40"/>
-      <c r="F21" s="40"/>
-      <c r="G21" s="22"/>
-      <c r="H21" s="42"/>
-      <c r="J21" s="81"/>
-      <c r="K21" s="82"/>
-      <c r="L21" s="82"/>
-      <c r="M21" s="82"/>
-      <c r="N21" s="82"/>
-      <c r="O21" s="83"/>
-      <c r="AK21" s="6">
+      <c r="D21" s="43"/>
+      <c r="E21" s="41"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="42"/>
+      <c r="H21" s="47"/>
+      <c r="J21" s="76"/>
+      <c r="K21" s="77"/>
+      <c r="L21" s="77"/>
+      <c r="M21" s="77"/>
+      <c r="N21" s="77"/>
+      <c r="O21" s="78"/>
+      <c r="AK21" s="4">
         <f t="shared" si="1"/>
         <v>7051</v>
       </c>
     </row>
     <row r="22" spans="1:37">
-      <c r="A22" s="8">
+      <c r="A22" s="6">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B22" s="13" t="str">
+      <c r="B22" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D32,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="J22" s="81"/>
-      <c r="K22" s="82"/>
-      <c r="L22" s="82"/>
-      <c r="M22" s="82"/>
-      <c r="N22" s="82"/>
-      <c r="O22" s="83"/>
-      <c r="AK22" s="6">
+      <c r="J22" s="76"/>
+      <c r="K22" s="77"/>
+      <c r="L22" s="77"/>
+      <c r="M22" s="77"/>
+      <c r="N22" s="77"/>
+      <c r="O22" s="78"/>
+      <c r="AK22" s="4">
         <f t="shared" si="1"/>
         <v>7124</v>
       </c>
     </row>
     <row r="23" spans="1:37" ht="14.45" customHeight="1" thickBot="1">
-      <c r="A23" s="8">
+      <c r="A23" s="6">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B23" s="13" t="str">
+      <c r="B23" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D33,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="J23" s="84"/>
-      <c r="K23" s="85"/>
-      <c r="L23" s="85"/>
-      <c r="M23" s="85"/>
-      <c r="N23" s="85"/>
-      <c r="O23" s="86"/>
-      <c r="AK23" s="6">
+      <c r="J23" s="80"/>
+      <c r="K23" s="81"/>
+      <c r="L23" s="81"/>
+      <c r="M23" s="81"/>
+      <c r="N23" s="81"/>
+      <c r="O23" s="82"/>
+      <c r="AK23" s="4">
         <f t="shared" si="1"/>
         <v>7961</v>
       </c>
     </row>
     <row r="24" spans="1:37">
-      <c r="A24" s="8">
+      <c r="A24" s="6">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B24" s="13" t="str">
+      <c r="B24" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D34,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D24" s="66" t="s">
+      <c r="D24" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="E24" s="67"/>
-      <c r="F24" s="67"/>
-      <c r="G24" s="67"/>
-      <c r="H24" s="68"/>
-      <c r="AK24" s="6">
+      <c r="E24" s="30"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="31"/>
+      <c r="AK24" s="4">
         <f t="shared" si="1"/>
         <v>1978</v>
       </c>
     </row>
     <row r="25" spans="1:37">
-      <c r="A25" s="8">
+      <c r="A25" s="6">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B25" s="13" t="str">
+      <c r="B25" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D35,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D25" s="69"/>
-      <c r="E25" s="70"/>
-      <c r="F25" s="70"/>
-      <c r="G25" s="70"/>
-      <c r="H25" s="71"/>
-      <c r="AK25" s="6">
+      <c r="D25" s="32"/>
+      <c r="E25" s="33"/>
+      <c r="F25" s="33"/>
+      <c r="G25" s="33"/>
+      <c r="H25" s="34"/>
+      <c r="AK25" s="4">
         <f t="shared" si="1"/>
         <v>1603</v>
       </c>
     </row>
     <row r="26" spans="1:37">
-      <c r="A26" s="8">
+      <c r="A26" s="6">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B26" s="13" t="str">
+      <c r="B26" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D36,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D26" s="69"/>
-      <c r="E26" s="70"/>
-      <c r="F26" s="70"/>
-      <c r="G26" s="70"/>
-      <c r="H26" s="71"/>
-      <c r="AK26" s="6">
+      <c r="D26" s="32"/>
+      <c r="E26" s="33"/>
+      <c r="F26" s="33"/>
+      <c r="G26" s="33"/>
+      <c r="H26" s="34"/>
+      <c r="AK26" s="4">
         <f t="shared" si="1"/>
         <v>8360</v>
       </c>
     </row>
     <row r="27" spans="1:37" ht="15.75" thickBot="1">
-      <c r="A27" s="8">
+      <c r="A27" s="6">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B27" s="13" t="str">
+      <c r="B27" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D37,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D27" s="72"/>
-      <c r="E27" s="73"/>
-      <c r="F27" s="73"/>
-      <c r="G27" s="73"/>
-      <c r="H27" s="74"/>
-      <c r="AK27" s="6">
+      <c r="D27" s="35"/>
+      <c r="E27" s="36"/>
+      <c r="F27" s="36"/>
+      <c r="G27" s="36"/>
+      <c r="H27" s="37"/>
+      <c r="AK27" s="4">
         <f t="shared" si="1"/>
         <v>145</v>
       </c>
     </row>
     <row r="28" spans="1:37" ht="15.75" thickBot="1">
-      <c r="A28" s="8">
+      <c r="A28" s="6">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="B28" s="13" t="str">
+      <c r="B28" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D38,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK28" s="6">
+      <c r="AK28" s="4">
         <f t="shared" si="1"/>
         <v>438</v>
       </c>
     </row>
     <row r="29" spans="1:37">
-      <c r="A29" s="8">
+      <c r="A29" s="6">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="B29" s="13" t="str">
+      <c r="B29" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D39,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D29" s="55" t="s">
+      <c r="D29" s="83" t="s">
         <v>37</v>
       </c>
-      <c r="E29" s="56"/>
-      <c r="F29" s="56"/>
-      <c r="G29" s="56"/>
-      <c r="H29" s="57"/>
-      <c r="AK29" s="6">
+      <c r="E29" s="84"/>
+      <c r="F29" s="84"/>
+      <c r="G29" s="84"/>
+      <c r="H29" s="85"/>
+      <c r="AK29" s="4">
         <f t="shared" si="1"/>
         <v>8195</v>
       </c>
     </row>
     <row r="30" spans="1:37">
-      <c r="A30" s="8">
+      <c r="A30" s="6">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="B30" s="13" t="str">
+      <c r="B30" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D40,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D30" s="58"/>
-      <c r="E30" s="59"/>
-      <c r="F30" s="59"/>
-      <c r="G30" s="59"/>
-      <c r="H30" s="60"/>
-      <c r="AK30" s="6">
+      <c r="D30" s="86"/>
+      <c r="E30" s="87"/>
+      <c r="F30" s="87"/>
+      <c r="G30" s="87"/>
+      <c r="H30" s="88"/>
+      <c r="AK30" s="4">
         <f t="shared" si="1"/>
         <v>6420</v>
       </c>
     </row>
     <row r="31" spans="1:37">
-      <c r="A31" s="8">
+      <c r="A31" s="6">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="B31" s="13" t="str">
+      <c r="B31" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D41,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D31" s="58"/>
-      <c r="E31" s="59"/>
-      <c r="F31" s="59"/>
-      <c r="G31" s="59"/>
-      <c r="H31" s="60"/>
-      <c r="AK31" s="6">
+      <c r="D31" s="86"/>
+      <c r="E31" s="87"/>
+      <c r="F31" s="87"/>
+      <c r="G31" s="87"/>
+      <c r="H31" s="88"/>
+      <c r="AK31" s="4">
         <f t="shared" si="1"/>
         <v>4161</v>
       </c>
     </row>
     <row r="32" spans="1:37">
-      <c r="A32" s="8">
+      <c r="A32" s="6">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B32" s="13" t="str">
+      <c r="B32" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D42,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D32" s="58"/>
-      <c r="E32" s="59"/>
-      <c r="F32" s="59"/>
-      <c r="G32" s="59"/>
-      <c r="H32" s="60"/>
-      <c r="AK32" s="6">
+      <c r="D32" s="86"/>
+      <c r="E32" s="87"/>
+      <c r="F32" s="87"/>
+      <c r="G32" s="87"/>
+      <c r="H32" s="88"/>
+      <c r="AK32" s="4">
         <f t="shared" si="1"/>
         <v>5022</v>
       </c>
     </row>
     <row r="33" spans="1:37">
-      <c r="A33" s="8">
+      <c r="A33" s="6">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="B33" s="13" t="str">
+      <c r="B33" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D43,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D33" s="58"/>
-      <c r="E33" s="59"/>
-      <c r="F33" s="59"/>
-      <c r="G33" s="59"/>
-      <c r="H33" s="60"/>
-      <c r="AK33" s="6">
+      <c r="D33" s="86"/>
+      <c r="E33" s="87"/>
+      <c r="F33" s="87"/>
+      <c r="G33" s="87"/>
+      <c r="H33" s="88"/>
+      <c r="AK33" s="4">
         <f t="shared" si="1"/>
         <v>3963</v>
       </c>
     </row>
     <row r="34" spans="1:37">
-      <c r="A34" s="8">
+      <c r="A34" s="6">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="B34" s="13" t="str">
+      <c r="B34" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D44,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D34" s="58"/>
-      <c r="E34" s="59"/>
-      <c r="F34" s="59"/>
-      <c r="G34" s="59"/>
-      <c r="H34" s="60"/>
-      <c r="AK34" s="6">
+      <c r="D34" s="86"/>
+      <c r="E34" s="87"/>
+      <c r="F34" s="87"/>
+      <c r="G34" s="87"/>
+      <c r="H34" s="88"/>
+      <c r="AK34" s="4">
         <f t="shared" si="1"/>
         <v>3380</v>
       </c>
     </row>
     <row r="35" spans="1:37">
-      <c r="A35" s="8">
+      <c r="A35" s="6">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="B35" s="13" t="str">
+      <c r="B35" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D45,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D35" s="58"/>
-      <c r="E35" s="59"/>
-      <c r="F35" s="59"/>
-      <c r="G35" s="59"/>
-      <c r="H35" s="60"/>
-      <c r="AK35" s="6">
+      <c r="D35" s="86"/>
+      <c r="E35" s="87"/>
+      <c r="F35" s="87"/>
+      <c r="G35" s="87"/>
+      <c r="H35" s="88"/>
+      <c r="AK35" s="4">
         <f t="shared" si="1"/>
         <v>1093</v>
       </c>
     </row>
     <row r="36" spans="1:37">
-      <c r="A36" s="8">
+      <c r="A36" s="6">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="B36" s="13" t="str">
+      <c r="B36" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D46,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D36" s="58"/>
-      <c r="E36" s="59"/>
-      <c r="F36" s="59"/>
-      <c r="G36" s="59"/>
-      <c r="H36" s="60"/>
-      <c r="AK36" s="6">
+      <c r="D36" s="86"/>
+      <c r="E36" s="87"/>
+      <c r="F36" s="87"/>
+      <c r="G36" s="87"/>
+      <c r="H36" s="88"/>
+      <c r="AK36" s="4">
         <f t="shared" si="1"/>
         <v>6910</v>
       </c>
     </row>
     <row r="37" spans="1:37">
-      <c r="A37" s="8">
+      <c r="A37" s="6">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="B37" s="13" t="str">
+      <c r="B37" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D47,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D37" s="58"/>
-      <c r="E37" s="59"/>
-      <c r="F37" s="59"/>
-      <c r="G37" s="59"/>
-      <c r="H37" s="60"/>
-      <c r="AK37" s="6">
+      <c r="D37" s="86"/>
+      <c r="E37" s="87"/>
+      <c r="F37" s="87"/>
+      <c r="G37" s="87"/>
+      <c r="H37" s="88"/>
+      <c r="AK37" s="4">
         <f t="shared" si="1"/>
         <v>9151</v>
       </c>
     </row>
     <row r="38" spans="1:37">
-      <c r="A38" s="8">
+      <c r="A38" s="6">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="B38" s="13" t="str">
+      <c r="B38" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D48,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D38" s="58"/>
-      <c r="E38" s="59"/>
-      <c r="F38" s="59"/>
-      <c r="G38" s="59"/>
-      <c r="H38" s="60"/>
-      <c r="AK38" s="6">
+      <c r="D38" s="86"/>
+      <c r="E38" s="87"/>
+      <c r="F38" s="87"/>
+      <c r="G38" s="87"/>
+      <c r="H38" s="88"/>
+      <c r="AK38" s="4">
         <f t="shared" si="1"/>
         <v>2304</v>
       </c>
     </row>
     <row r="39" spans="1:37">
-      <c r="A39" s="8">
+      <c r="A39" s="6">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="B39" s="13" t="str">
+      <c r="B39" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D49,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D39" s="58"/>
-      <c r="E39" s="59"/>
-      <c r="F39" s="59"/>
-      <c r="G39" s="59"/>
-      <c r="H39" s="60"/>
-      <c r="AK39" s="6">
+      <c r="D39" s="86"/>
+      <c r="E39" s="87"/>
+      <c r="F39" s="87"/>
+      <c r="G39" s="87"/>
+      <c r="H39" s="88"/>
+      <c r="AK39" s="4">
         <f t="shared" si="1"/>
         <v>8105</v>
       </c>
     </row>
     <row r="40" spans="1:37" ht="15.75" thickBot="1">
-      <c r="A40" s="8">
+      <c r="A40" s="6">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="B40" s="13" t="str">
+      <c r="B40" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D50,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D40" s="61"/>
-      <c r="E40" s="62"/>
-      <c r="F40" s="62"/>
-      <c r="G40" s="62"/>
-      <c r="H40" s="63"/>
-      <c r="AK40" s="6">
+      <c r="D40" s="89"/>
+      <c r="E40" s="90"/>
+      <c r="F40" s="90"/>
+      <c r="G40" s="90"/>
+      <c r="H40" s="91"/>
+      <c r="AK40" s="4">
         <f t="shared" si="1"/>
         <v>4006</v>
       </c>
     </row>
     <row r="41" spans="1:37">
-      <c r="A41" s="8">
+      <c r="A41" s="6">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="B41" s="13" t="str">
+      <c r="B41" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D51,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK41" s="6">
+      <c r="AK41" s="4">
         <f t="shared" si="1"/>
         <v>355</v>
       </c>
     </row>
     <row r="42" spans="1:37">
-      <c r="A42" s="8">
+      <c r="A42" s="6">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="B42" s="13" t="str">
+      <c r="B42" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D52,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK42" s="6">
+      <c r="AK42" s="4">
         <f t="shared" si="1"/>
         <v>9128</v>
       </c>
     </row>
     <row r="43" spans="1:37">
-      <c r="A43" s="8">
+      <c r="A43" s="6">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="B43" s="13" t="str">
+      <c r="B43" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D53,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK43" s="6">
+      <c r="AK43" s="4">
         <f t="shared" si="1"/>
         <v>1789</v>
       </c>
     </row>
     <row r="44" spans="1:37">
-      <c r="A44" s="8">
+      <c r="A44" s="6">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="B44" s="13" t="str">
+      <c r="B44" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D54,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK44" s="6">
+      <c r="AK44" s="4">
         <f t="shared" si="1"/>
         <v>2954</v>
       </c>
     </row>
     <row r="45" spans="1:37">
-      <c r="A45" s="8">
+      <c r="A45" s="6">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="B45" s="13" t="str">
+      <c r="B45" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D55,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK45" s="6">
+      <c r="AK45" s="4">
         <f t="shared" si="1"/>
         <v>3119</v>
       </c>
     </row>
     <row r="46" spans="1:37">
-      <c r="A46" s="8">
+      <c r="A46" s="6">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="B46" s="13" t="str">
+      <c r="B46" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D56,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK46" s="6">
+      <c r="AK46" s="4">
         <f t="shared" si="1"/>
         <v>6016</v>
       </c>
     </row>
     <row r="47" spans="1:37">
-      <c r="A47" s="8">
+      <c r="A47" s="6">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="B47" s="13" t="str">
+      <c r="B47" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D57,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK47" s="6">
+      <c r="AK47" s="4">
         <f t="shared" si="1"/>
         <v>2293</v>
       </c>
     </row>
     <row r="48" spans="1:37">
-      <c r="A48" s="8">
+      <c r="A48" s="6">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="B48" s="13" t="str">
+      <c r="B48" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D58,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK48" s="6">
+      <c r="AK48" s="4">
         <f t="shared" si="1"/>
         <v>5466</v>
       </c>
     </row>
     <row r="49" spans="1:37">
-      <c r="A49" s="8">
+      <c r="A49" s="6">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="B49" s="13" t="str">
+      <c r="B49" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D59,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK49" s="6">
+      <c r="AK49" s="4">
         <f t="shared" si="1"/>
         <v>7923</v>
       </c>
     </row>
     <row r="50" spans="1:37">
-      <c r="A50" s="8">
+      <c r="A50" s="6">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="B50" s="13" t="str">
+      <c r="B50" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D60,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK50" s="6">
+      <c r="AK50" s="4">
         <f t="shared" si="1"/>
         <v>8704</v>
       </c>
     </row>
     <row r="51" spans="1:37">
-      <c r="A51" s="8">
+      <c r="A51" s="6">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="B51" s="13" t="str">
+      <c r="B51" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D61,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK51" s="6">
+      <c r="AK51" s="4">
         <f t="shared" si="1"/>
         <v>3461</v>
       </c>
     </row>
     <row r="52" spans="1:37">
-      <c r="A52" s="8">
+      <c r="A52" s="6">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="B52" s="13" t="str">
+      <c r="B52" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D62,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK52" s="6">
+      <c r="AK52" s="4">
         <f t="shared" si="1"/>
         <v>514</v>
       </c>
     </row>
     <row r="53" spans="1:37">
-      <c r="A53" s="8">
+      <c r="A53" s="6">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="B53" s="13" t="str">
+      <c r="B53" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D63,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK53" s="6">
+      <c r="AK53" s="4">
         <f t="shared" si="1"/>
         <v>3915</v>
       </c>
     </row>
     <row r="54" spans="1:37">
-      <c r="A54" s="8">
+      <c r="A54" s="6">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="B54" s="13" t="str">
+      <c r="B54" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D64,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK54" s="6">
+      <c r="AK54" s="4">
         <f t="shared" si="1"/>
         <v>2704</v>
       </c>
     </row>
     <row r="55" spans="1:37">
-      <c r="A55" s="8">
+      <c r="A55" s="6">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="B55" s="13" t="str">
+      <c r="B55" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D65,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK55" s="6">
+      <c r="AK55" s="4">
         <f t="shared" si="1"/>
         <v>1509</v>
       </c>
     </row>
     <row r="56" spans="1:37">
-      <c r="A56" s="8">
+      <c r="A56" s="6">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="B56" s="13" t="str">
+      <c r="B56" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D66,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK56" s="6">
+      <c r="AK56" s="4">
         <f t="shared" si="1"/>
         <v>6654</v>
       </c>
     </row>
     <row r="57" spans="1:37">
-      <c r="A57" s="8">
+      <c r="A57" s="6">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="B57" s="13" t="str">
+      <c r="B57" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D67,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK57" s="6">
+      <c r="AK57" s="4">
         <f t="shared" si="1"/>
         <v>8603</v>
       </c>
     </row>
     <row r="58" spans="1:37">
-      <c r="A58" s="8">
+      <c r="A58" s="6">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
-      <c r="B58" s="13" t="str">
+      <c r="B58" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D68,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK58" s="6">
+      <c r="AK58" s="4">
         <f t="shared" si="1"/>
         <v>7580</v>
       </c>
     </row>
     <row r="59" spans="1:37">
-      <c r="A59" s="8">
+      <c r="A59" s="6">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="B59" s="13" t="str">
+      <c r="B59" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D69,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK59" s="6">
+      <c r="AK59" s="4">
         <f t="shared" si="1"/>
         <v>625</v>
       </c>
     </row>
     <row r="60" spans="1:37">
-      <c r="A60" s="8">
+      <c r="A60" s="6">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
-      <c r="B60" s="13" t="str">
+      <c r="B60" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D70,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK60" s="6">
+      <c r="AK60" s="4">
         <f t="shared" si="1"/>
         <v>7198</v>
       </c>
     </row>
     <row r="61" spans="1:37">
-      <c r="A61" s="8">
+      <c r="A61" s="6">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="B61" s="13" t="str">
+      <c r="B61" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D71,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK61" s="6">
+      <c r="AK61" s="4">
         <f t="shared" si="1"/>
         <v>4035</v>
       </c>
     </row>
     <row r="62" spans="1:37">
-      <c r="A62" s="8">
+      <c r="A62" s="6">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="B62" s="13" t="str">
+      <c r="B62" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D72,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK62" s="6">
+      <c r="AK62" s="4">
         <f t="shared" si="1"/>
         <v>8980</v>
       </c>
     </row>
     <row r="63" spans="1:37">
-      <c r="A63" s="8">
+      <c r="A63" s="6">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="B63" s="13" t="str">
+      <c r="B63" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D73,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK63" s="6">
+      <c r="AK63" s="4">
         <f t="shared" si="1"/>
         <v>469</v>
       </c>
     </row>
     <row r="64" spans="1:37">
-      <c r="A64" s="8">
+      <c r="A64" s="6">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="B64" s="13" t="str">
+      <c r="B64" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D74,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK64" s="6">
+      <c r="AK64" s="4">
         <f t="shared" si="1"/>
         <v>7294</v>
       </c>
     </row>
     <row r="65" spans="1:37">
-      <c r="A65" s="8">
+      <c r="A65" s="6">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="B65" s="13" t="str">
+      <c r="B65" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D75,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK65" s="6">
+      <c r="AK65" s="4">
         <f t="shared" si="1"/>
         <v>5387</v>
       </c>
     </row>
     <row r="66" spans="1:37">
-      <c r="A66" s="8">
+      <c r="A66" s="6">
         <f t="shared" si="0"/>
         <v>65</v>
       </c>
-      <c r="B66" s="13" t="str">
+      <c r="B66" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D76,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK66" s="6">
+      <c r="AK66" s="4">
         <f t="shared" si="1"/>
         <v>8148</v>
       </c>
     </row>
     <row r="67" spans="1:37">
-      <c r="A67" s="8">
+      <c r="A67" s="6">
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
-      <c r="B67" s="13" t="str">
+      <c r="B67" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D77,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK67" s="6">
+      <c r="AK67" s="4">
         <f t="shared" si="1"/>
         <v>981</v>
       </c>
     </row>
     <row r="68" spans="1:37">
-      <c r="A68" s="8">
+      <c r="A68" s="6">
         <f t="shared" ref="A68:A103" si="2">A67+1</f>
         <v>67</v>
       </c>
-      <c r="B68" s="13" t="str">
+      <c r="B68" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D78,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK68" s="6">
+      <c r="AK68" s="4">
         <f t="shared" ref="AK68:AK103" si="3">MOD(AK67*1103515245 + 12345,9172)</f>
         <v>8390</v>
       </c>
     </row>
     <row r="69" spans="1:37">
-      <c r="A69" s="8">
+      <c r="A69" s="6">
         <f t="shared" si="2"/>
         <v>68</v>
       </c>
-      <c r="B69" s="13" t="str">
+      <c r="B69" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D79,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK69" s="6">
+      <c r="AK69" s="4">
         <f t="shared" si="3"/>
         <v>4007</v>
       </c>
     </row>
     <row r="70" spans="1:37">
-      <c r="A70" s="8">
+      <c r="A70" s="6">
         <f t="shared" si="2"/>
         <v>69</v>
       </c>
-      <c r="B70" s="13" t="str">
+      <c r="B70" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D80,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK70" s="6">
+      <c r="AK70" s="4">
         <f t="shared" si="3"/>
         <v>4764</v>
       </c>
     </row>
     <row r="71" spans="1:37">
-      <c r="A71" s="8">
+      <c r="A71" s="6">
         <f t="shared" si="2"/>
         <v>70</v>
       </c>
-      <c r="B71" s="13" t="str">
+      <c r="B71" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D81,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK71" s="6">
+      <c r="AK71" s="4">
         <f t="shared" si="3"/>
         <v>3769</v>
       </c>
     </row>
     <row r="72" spans="1:37">
-      <c r="A72" s="8">
+      <c r="A72" s="6">
         <f t="shared" si="2"/>
         <v>71</v>
       </c>
-      <c r="B72" s="13" t="str">
+      <c r="B72" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D82,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK72" s="6">
+      <c r="AK72" s="4">
         <f t="shared" si="3"/>
         <v>1030</v>
       </c>
     </row>
     <row r="73" spans="1:37">
-      <c r="A73" s="8">
+      <c r="A73" s="6">
         <f t="shared" si="2"/>
         <v>72</v>
       </c>
-      <c r="B73" s="13" t="str">
+      <c r="B73" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D83,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK73" s="6">
+      <c r="AK73" s="4">
         <f t="shared" si="3"/>
         <v>4303</v>
       </c>
     </row>
     <row r="74" spans="1:37">
-      <c r="A74" s="8">
+      <c r="A74" s="6">
         <f t="shared" si="2"/>
         <v>73</v>
       </c>
-      <c r="B74" s="13" t="str">
+      <c r="B74" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D84,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK74" s="6">
+      <c r="AK74" s="4">
         <f t="shared" si="3"/>
         <v>7404</v>
       </c>
     </row>
     <row r="75" spans="1:37">
-      <c r="A75" s="8">
+      <c r="A75" s="6">
         <f t="shared" si="2"/>
         <v>74</v>
       </c>
-      <c r="B75" s="13" t="str">
+      <c r="B75" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D85,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK75" s="6">
+      <c r="AK75" s="4">
         <f t="shared" si="3"/>
         <v>4261</v>
       </c>
     </row>
     <row r="76" spans="1:37">
-      <c r="A76" s="8">
+      <c r="A76" s="6">
         <f t="shared" si="2"/>
         <v>75</v>
       </c>
-      <c r="B76" s="13" t="str">
+      <c r="B76" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D86,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK76" s="6">
+      <c r="AK76" s="4">
         <f t="shared" si="3"/>
         <v>5666</v>
       </c>
     </row>
     <row r="77" spans="1:37">
-      <c r="A77" s="8">
+      <c r="A77" s="6">
         <f t="shared" si="2"/>
         <v>76</v>
       </c>
-      <c r="B77" s="13" t="str">
+      <c r="B77" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D87,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK77" s="6">
+      <c r="AK77" s="4">
         <f t="shared" si="3"/>
         <v>39</v>
       </c>
     </row>
     <row r="78" spans="1:37">
-      <c r="A78" s="8">
+      <c r="A78" s="6">
         <f t="shared" si="2"/>
         <v>77</v>
       </c>
-      <c r="B78" s="13" t="str">
+      <c r="B78" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D88,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK78" s="6">
+      <c r="AK78" s="4">
         <f t="shared" si="3"/>
         <v>856</v>
       </c>
     </row>
     <row r="79" spans="1:37">
-      <c r="A79" s="8">
+      <c r="A79" s="6">
         <f t="shared" si="2"/>
         <v>78</v>
       </c>
-      <c r="B79" s="13" t="str">
+      <c r="B79" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D89,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK79" s="6">
+      <c r="AK79" s="4">
         <f t="shared" si="3"/>
         <v>7585</v>
       </c>
     </row>
     <row r="80" spans="1:37">
-      <c r="A80" s="8">
+      <c r="A80" s="6">
         <f t="shared" si="2"/>
         <v>79</v>
       </c>
-      <c r="B80" s="13" t="str">
+      <c r="B80" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D90,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK80" s="6">
+      <c r="AK80" s="4">
         <f t="shared" si="3"/>
         <v>4326</v>
       </c>
     </row>
     <row r="81" spans="1:37">
-      <c r="A81" s="8">
+      <c r="A81" s="6">
         <f t="shared" si="2"/>
         <v>80</v>
       </c>
-      <c r="B81" s="13" t="str">
+      <c r="B81" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D91,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK81" s="6">
+      <c r="AK81" s="4">
         <f t="shared" si="3"/>
         <v>7919</v>
       </c>
     </row>
     <row r="82" spans="1:37">
-      <c r="A82" s="8">
+      <c r="A82" s="6">
         <f t="shared" si="2"/>
         <v>81</v>
       </c>
-      <c r="B82" s="13" t="str">
+      <c r="B82" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D92,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK82" s="6">
+      <c r="AK82" s="4">
         <f t="shared" si="3"/>
         <v>240</v>
       </c>
     </row>
     <row r="83" spans="1:37">
-      <c r="A83" s="8">
+      <c r="A83" s="6">
         <f t="shared" si="2"/>
         <v>82</v>
       </c>
-      <c r="B83" s="13" t="str">
+      <c r="B83" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D93,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK83" s="6">
+      <c r="AK83" s="4">
         <f t="shared" si="3"/>
         <v>6553</v>
       </c>
     </row>
     <row r="84" spans="1:37">
-      <c r="A84" s="8">
+      <c r="A84" s="6">
         <f t="shared" si="2"/>
         <v>83</v>
       </c>
-      <c r="B84" s="13" t="str">
+      <c r="B84" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D94,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK84" s="6">
+      <c r="AK84" s="4">
         <f t="shared" si="3"/>
         <v>3550</v>
       </c>
     </row>
     <row r="85" spans="1:37">
-      <c r="A85" s="8">
+      <c r="A85" s="6">
         <f t="shared" si="2"/>
         <v>84</v>
       </c>
-      <c r="B85" s="13" t="str">
+      <c r="B85" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D95,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK85" s="6">
+      <c r="AK85" s="4">
         <f t="shared" si="3"/>
         <v>7691</v>
       </c>
     </row>
     <row r="86" spans="1:37">
-      <c r="A86" s="8">
+      <c r="A86" s="6">
         <f t="shared" si="2"/>
         <v>85</v>
       </c>
-      <c r="B86" s="13" t="str">
+      <c r="B86" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D96,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK86" s="6">
+      <c r="AK86" s="4">
         <f t="shared" si="3"/>
         <v>3908</v>
       </c>
     </row>
     <row r="87" spans="1:37">
-      <c r="A87" s="8">
+      <c r="A87" s="6">
         <f t="shared" si="2"/>
         <v>86</v>
       </c>
-      <c r="B87" s="13" t="str">
+      <c r="B87" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D97,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK87" s="6">
+      <c r="AK87" s="4">
         <f t="shared" si="3"/>
         <v>8529</v>
       </c>
     </row>
     <row r="88" spans="1:37">
-      <c r="A88" s="8">
+      <c r="A88" s="6">
         <f t="shared" si="2"/>
         <v>87</v>
       </c>
-      <c r="B88" s="13" t="str">
+      <c r="B88" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D98,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK88" s="6">
+      <c r="AK88" s="4">
         <f t="shared" si="3"/>
         <v>2334</v>
       </c>
     </row>
     <row r="89" spans="1:37">
-      <c r="A89" s="8">
+      <c r="A89" s="6">
         <f t="shared" si="2"/>
         <v>88</v>
       </c>
-      <c r="B89" s="13" t="str">
+      <c r="B89" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D99,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK89" s="6">
+      <c r="AK89" s="4">
         <f t="shared" si="3"/>
         <v>2795</v>
       </c>
     </row>
     <row r="90" spans="1:37">
-      <c r="A90" s="8">
+      <c r="A90" s="6">
         <f t="shared" si="2"/>
         <v>89</v>
       </c>
-      <c r="B90" s="13" t="str">
+      <c r="B90" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D100,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK90" s="6">
+      <c r="AK90" s="4">
         <f t="shared" si="3"/>
         <v>8332</v>
       </c>
     </row>
     <row r="91" spans="1:37">
-      <c r="A91" s="8">
+      <c r="A91" s="6">
         <f t="shared" si="2"/>
         <v>90</v>
       </c>
-      <c r="B91" s="13" t="str">
+      <c r="B91" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D101,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK91" s="6">
+      <c r="AK91" s="4">
         <f t="shared" si="3"/>
         <v>5101</v>
       </c>
     </row>
     <row r="92" spans="1:37">
-      <c r="A92" s="8">
+      <c r="A92" s="6">
         <f t="shared" si="2"/>
         <v>91</v>
       </c>
-      <c r="B92" s="13" t="str">
+      <c r="B92" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D102,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK92" s="6">
+      <c r="AK92" s="4">
         <f t="shared" si="3"/>
         <v>3738</v>
       </c>
     </row>
     <row r="93" spans="1:37">
-      <c r="A93" s="8">
+      <c r="A93" s="6">
         <f t="shared" si="2"/>
         <v>92</v>
       </c>
-      <c r="B93" s="13" t="str">
+      <c r="B93" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D103,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK93" s="6">
+      <c r="AK93" s="4">
         <f t="shared" si="3"/>
         <v>1931</v>
       </c>
     </row>
     <row r="94" spans="1:37">
-      <c r="A94" s="8">
+      <c r="A94" s="6">
         <f t="shared" si="2"/>
         <v>93</v>
       </c>
-      <c r="B94" s="13" t="str">
+      <c r="B94" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D104,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK94" s="6">
+      <c r="AK94" s="4">
         <f t="shared" si="3"/>
         <v>5336</v>
       </c>
     </row>
     <row r="95" spans="1:37">
-      <c r="A95" s="8">
+      <c r="A95" s="6">
         <f t="shared" si="2"/>
         <v>94</v>
       </c>
-      <c r="B95" s="13" t="str">
+      <c r="B95" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D105,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK95" s="6">
+      <c r="AK95" s="4">
         <f t="shared" si="3"/>
         <v>3417</v>
       </c>
     </row>
     <row r="96" spans="1:37">
-      <c r="A96" s="8">
+      <c r="A96" s="6">
         <f t="shared" si="2"/>
         <v>95</v>
       </c>
-      <c r="B96" s="13" t="str">
+      <c r="B96" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D106,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK96" s="6">
+      <c r="AK96" s="4">
         <f t="shared" si="3"/>
         <v>8302</v>
       </c>
     </row>
     <row r="97" spans="1:37">
-      <c r="A97" s="8">
+      <c r="A97" s="6">
         <f t="shared" si="2"/>
         <v>96</v>
       </c>
-      <c r="B97" s="13" t="str">
+      <c r="B97" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D107,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK97" s="6">
+      <c r="AK97" s="4">
         <f t="shared" si="3"/>
         <v>1239</v>
       </c>
     </row>
     <row r="98" spans="1:37">
-      <c r="A98" s="8">
+      <c r="A98" s="6">
         <f t="shared" si="2"/>
         <v>97</v>
       </c>
-      <c r="B98" s="13" t="str">
+      <c r="B98" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D108,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK98" s="6">
+      <c r="AK98" s="4">
         <f t="shared" si="3"/>
         <v>8584</v>
       </c>
     </row>
     <row r="99" spans="1:37">
-      <c r="A99" s="8">
+      <c r="A99" s="6">
         <f t="shared" si="2"/>
         <v>98</v>
       </c>
-      <c r="B99" s="13" t="str">
+      <c r="B99" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D109,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK99" s="6">
+      <c r="AK99" s="4">
         <f t="shared" si="3"/>
         <v>6357</v>
       </c>
     </row>
     <row r="100" spans="1:37">
-      <c r="A100" s="8">
+      <c r="A100" s="6">
         <f t="shared" si="2"/>
         <v>99</v>
       </c>
-      <c r="B100" s="13" t="str">
+      <c r="B100" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D110,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK100" s="6">
+      <c r="AK100" s="4">
         <f t="shared" si="3"/>
         <v>1554</v>
       </c>
     </row>
     <row r="101" spans="1:37">
-      <c r="A101" s="8">
+      <c r="A101" s="6">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="B101" s="13" t="str">
+      <c r="B101" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D111,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK101" s="6">
+      <c r="AK101" s="4">
         <f t="shared" si="3"/>
         <v>3275</v>
       </c>
     </row>
     <row r="102" spans="1:37">
-      <c r="A102" s="8">
+      <c r="A102" s="6">
         <f t="shared" si="2"/>
         <v>101</v>
       </c>
-      <c r="B102" s="13" t="str">
+      <c r="B102" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D112,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK102" s="6">
+      <c r="AK102" s="4">
         <f t="shared" si="3"/>
         <v>5920</v>
       </c>
     </row>
     <row r="103" spans="1:37">
-      <c r="A103" s="8">
+      <c r="A103" s="6">
         <f t="shared" si="2"/>
         <v>102</v>
       </c>
-      <c r="B103" s="13" t="str">
+      <c r="B103" s="6" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D113,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK103" s="6">
+      <c r="AK103" s="4">
         <f t="shared" si="3"/>
         <v>941</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection formatCells="0" formatColumns="0" insertColumns="0" insertHyperlinks="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="shV5KQ3KDtaAlSp8g0dplxHGzd++xSI5j3hh4m9CstAz0JMZbczwCPz6D+kzPG6LxxantyP+5vj8RxFaex+5rA==" saltValue="7JUfDB+dpbhXnwAvC5WpTw==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" insertColumns="0" insertHyperlinks="0"/>
   <dataConsolidate/>
   <customSheetViews>
     <customSheetView guid="{8A50E3A6-4261-4BD1-A94F-918D0E3EEAC3}" hiddenColumns="1">
@@ -4741,6 +4806,7 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId6"/>
+  <legacyDrawing r:id="rId7"/>
 </worksheet>
 </file>
 
@@ -5513,7 +5579,7 @@
       <c r="A13" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="5">
         <f t="shared" ref="B13:B76" ca="1" si="3">MOD(B12*F$11+F$12,F$13)</f>
         <v>22544</v>
       </c>
@@ -5588,7 +5654,7 @@
       <c r="A14" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>3849</v>
       </c>
@@ -5660,7 +5726,7 @@
       <c r="A15" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>21774</v>
       </c>
@@ -5732,7 +5798,7 @@
       <c r="A16" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>11055</v>
       </c>
@@ -5804,7 +5870,7 @@
       <c r="A17" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>25916</v>
       </c>
@@ -5876,7 +5942,7 @@
       <c r="A18" t="s">
         <v>45</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>4805</v>
       </c>
@@ -5897,7 +5963,7 @@
       <c r="A19" t="s">
         <v>46</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>13338</v>
       </c>
@@ -5918,7 +5984,7 @@
       <c r="A20" t="s">
         <v>47</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B20" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>19275</v>
       </c>
@@ -5939,7 +6005,7 @@
       <c r="A21" t="s">
         <v>48</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>6440</v>
       </c>
@@ -5960,7 +6026,7 @@
       <c r="A22" t="s">
         <v>49</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B22" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>5697</v>
       </c>
@@ -5976,13 +6042,13 @@
         <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
-      <c r="M22" s="10"/>
+      <c r="M22" s="5"/>
     </row>
     <row r="23" spans="1:23">
       <c r="A23" t="s">
         <v>50</v>
       </c>
-      <c r="B23" s="10">
+      <c r="B23" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>30694</v>
       </c>
@@ -5998,13 +6064,13 @@
         <f t="shared" ca="1" si="6"/>
         <v>4</v>
       </c>
-      <c r="M23" s="10"/>
+      <c r="M23" s="5"/>
     </row>
     <row r="24" spans="1:23">
       <c r="A24" t="s">
         <v>51</v>
       </c>
-      <c r="B24" s="10">
+      <c r="B24" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>20775</v>
       </c>
@@ -6020,13 +6086,13 @@
         <f t="shared" ca="1" si="6"/>
         <v>3</v>
       </c>
-      <c r="M24" s="10"/>
+      <c r="M24" s="5"/>
     </row>
     <row r="25" spans="1:23">
       <c r="A25" t="s">
         <v>52</v>
       </c>
-      <c r="B25" s="10">
+      <c r="B25" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>8148</v>
       </c>
@@ -6042,13 +6108,13 @@
         <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
-      <c r="M25" s="10"/>
+      <c r="M25" s="5"/>
     </row>
     <row r="26" spans="1:23">
       <c r="A26" t="s">
         <v>53</v>
       </c>
-      <c r="B26" s="10">
+      <c r="B26" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>21885</v>
       </c>
@@ -6064,13 +6130,13 @@
         <f t="shared" ca="1" si="6"/>
         <v>3</v>
       </c>
-      <c r="M26" s="10"/>
+      <c r="M26" s="5"/>
     </row>
     <row r="27" spans="1:23">
       <c r="A27" t="s">
         <v>54</v>
       </c>
-      <c r="B27" s="10">
+      <c r="B27" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>11378</v>
       </c>
@@ -6086,13 +6152,13 @@
         <f t="shared" ca="1" si="6"/>
         <v>1</v>
       </c>
-      <c r="M27" s="10"/>
+      <c r="M27" s="5"/>
     </row>
     <row r="28" spans="1:23">
       <c r="A28" t="s">
         <v>55</v>
       </c>
-      <c r="B28" s="10">
+      <c r="B28" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>22723</v>
       </c>
@@ -6108,13 +6174,13 @@
         <f t="shared" ca="1" si="6"/>
         <v>3</v>
       </c>
-      <c r="M28" s="10"/>
+      <c r="M28" s="5"/>
     </row>
     <row r="29" spans="1:23">
       <c r="A29" t="s">
         <v>56</v>
       </c>
-      <c r="B29" s="10">
+      <c r="B29" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>25920</v>
       </c>
@@ -6130,13 +6196,13 @@
         <f t="shared" ca="1" si="6"/>
         <v>4</v>
       </c>
-      <c r="M29" s="10"/>
+      <c r="M29" s="5"/>
     </row>
     <row r="30" spans="1:23">
       <c r="A30" t="s">
         <v>57</v>
       </c>
-      <c r="B30" s="10">
+      <c r="B30" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>19577</v>
       </c>
@@ -6152,13 +6218,13 @@
         <f t="shared" ca="1" si="6"/>
         <v>3</v>
       </c>
-      <c r="M30" s="10"/>
+      <c r="M30" s="5"/>
     </row>
     <row r="31" spans="1:23">
       <c r="A31" t="s">
         <v>58</v>
       </c>
-      <c r="B31" s="10">
+      <c r="B31" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>7614</v>
       </c>
@@ -6174,13 +6240,13 @@
         <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
-      <c r="M31" s="10"/>
+      <c r="M31" s="5"/>
     </row>
     <row r="32" spans="1:23">
       <c r="A32" t="s">
         <v>59</v>
       </c>
-      <c r="B32" s="10">
+      <c r="B32" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>15903</v>
       </c>
@@ -6196,13 +6262,13 @@
         <f t="shared" ca="1" si="6"/>
         <v>1</v>
       </c>
-      <c r="M32" s="10"/>
+      <c r="M32" s="5"/>
     </row>
     <row r="33" spans="1:13">
       <c r="A33" t="s">
         <v>60</v>
       </c>
-      <c r="B33" s="10">
+      <c r="B33" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>5484</v>
       </c>
@@ -6218,13 +6284,13 @@
         <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
-      <c r="M33" s="10"/>
+      <c r="M33" s="5"/>
     </row>
     <row r="34" spans="1:13">
       <c r="A34" t="s">
         <v>61</v>
       </c>
-      <c r="B34" s="10">
+      <c r="B34" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>14133</v>
       </c>
@@ -6245,7 +6311,7 @@
       <c r="A35" t="s">
         <v>62</v>
       </c>
-      <c r="B35" s="10">
+      <c r="B35" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>22474</v>
       </c>
@@ -6266,7 +6332,7 @@
       <c r="A36" t="s">
         <v>63</v>
       </c>
-      <c r="B36" s="10">
+      <c r="B36" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>7483</v>
       </c>
@@ -6287,7 +6353,7 @@
       <c r="A37" t="s">
         <v>64</v>
       </c>
-      <c r="B37" s="10">
+      <c r="B37" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>7256</v>
       </c>
@@ -6308,7 +6374,7 @@
       <c r="A38" t="s">
         <v>65</v>
       </c>
-      <c r="B38" s="10">
+      <c r="B38" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>4529</v>
       </c>
@@ -6329,7 +6395,7 @@
       <c r="A39" t="s">
         <v>66</v>
       </c>
-      <c r="B39" s="10">
+      <c r="B39" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>9878</v>
       </c>
@@ -6350,7 +6416,7 @@
       <c r="A40" t="s">
         <v>67</v>
       </c>
-      <c r="B40" s="10">
+      <c r="B40" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>21015</v>
       </c>
@@ -6371,7 +6437,7 @@
       <c r="A41" t="s">
         <v>68</v>
       </c>
-      <c r="B41" s="10">
+      <c r="B41" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>9732</v>
       </c>
@@ -6392,7 +6458,7 @@
       <c r="A42" t="s">
         <v>69</v>
       </c>
-      <c r="B42" s="10">
+      <c r="B42" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>6125</v>
       </c>
@@ -6413,7 +6479,7 @@
       <c r="A43" t="s">
         <v>70</v>
       </c>
-      <c r="B43" s="10">
+      <c r="B43" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>5666</v>
       </c>
@@ -6434,7 +6500,7 @@
       <c r="A44" t="s">
         <v>71</v>
       </c>
-      <c r="B44" s="10">
+      <c r="B44" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>30899</v>
       </c>
@@ -6455,7 +6521,7 @@
       <c r="A45" t="s">
         <v>72</v>
       </c>
-      <c r="B45" s="10">
+      <c r="B45" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>7792</v>
       </c>
@@ -6476,7 +6542,7 @@
       <c r="A46" t="s">
         <v>73</v>
       </c>
-      <c r="B46" s="10">
+      <c r="B46" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>17897</v>
       </c>
@@ -6497,7 +6563,7 @@
       <c r="A47" t="s">
         <v>74</v>
       </c>
-      <c r="B47" s="10">
+      <c r="B47" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>29294</v>
       </c>
@@ -6518,7 +6584,7 @@
       <c r="A48" t="s">
         <v>75</v>
       </c>
-      <c r="B48" s="10">
+      <c r="B48" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>27919</v>
       </c>
@@ -6539,7 +6605,7 @@
       <c r="A49" t="s">
         <v>76</v>
       </c>
-      <c r="B49" s="10">
+      <c r="B49" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>12700</v>
       </c>
@@ -6560,7 +6626,7 @@
       <c r="A50" t="s">
         <v>77</v>
       </c>
-      <c r="B50" s="10">
+      <c r="B50" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>22437</v>
       </c>
@@ -6581,7 +6647,7 @@
       <c r="A51" t="s">
         <v>78</v>
       </c>
-      <c r="B51" s="10">
+      <c r="B51" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>18298</v>
       </c>
@@ -6602,7 +6668,7 @@
       <c r="A52" t="s">
         <v>79</v>
       </c>
-      <c r="B52" s="10">
+      <c r="B52" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>19243</v>
       </c>
@@ -6623,7 +6689,7 @@
       <c r="A53" t="s">
         <v>80</v>
       </c>
-      <c r="B53" s="10">
+      <c r="B53" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>19336</v>
       </c>
@@ -6644,7 +6710,7 @@
       <c r="A54" t="s">
         <v>81</v>
       </c>
-      <c r="B54" s="10">
+      <c r="B54" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>18721</v>
       </c>
@@ -6665,7 +6731,7 @@
       <c r="A55" t="s">
         <v>82</v>
       </c>
-      <c r="B55" s="10">
+      <c r="B55" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>24902</v>
       </c>
@@ -6686,7 +6752,7 @@
       <c r="A56" t="s">
         <v>83</v>
       </c>
-      <c r="B56" s="10">
+      <c r="B56" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>28423</v>
       </c>
@@ -6707,7 +6773,7 @@
       <c r="A57" t="s">
         <v>84</v>
       </c>
-      <c r="B57" s="10">
+      <c r="B57" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>6196</v>
       </c>
@@ -6728,7 +6794,7 @@
       <c r="A58" t="s">
         <v>85</v>
       </c>
-      <c r="B58" s="10">
+      <c r="B58" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>22109</v>
       </c>
@@ -6749,7 +6815,7 @@
       <c r="A59" t="s">
         <v>86</v>
       </c>
-      <c r="B59" s="10">
+      <c r="B59" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>19410</v>
       </c>
@@ -6770,7 +6836,7 @@
       <c r="A60" t="s">
         <v>87</v>
       </c>
-      <c r="B60" s="10">
+      <c r="B60" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>29859</v>
       </c>
@@ -6791,7 +6857,7 @@
       <c r="A61" t="s">
         <v>88</v>
       </c>
-      <c r="B61" s="10">
+      <c r="B61" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>928</v>
       </c>
@@ -6812,7 +6878,7 @@
       <c r="A62" t="s">
         <v>89</v>
       </c>
-      <c r="B62" s="10">
+      <c r="B62" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>31577</v>
       </c>
@@ -6833,7 +6899,7 @@
       <c r="A63" t="s">
         <v>90</v>
       </c>
-      <c r="B63" s="10">
+      <c r="B63" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>21278</v>
       </c>
@@ -6854,7 +6920,7 @@
       <c r="A64" t="s">
         <v>91</v>
       </c>
-      <c r="B64" s="10">
+      <c r="B64" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>14335</v>
       </c>
@@ -6875,7 +6941,7 @@
       <c r="A65" t="s">
         <v>92</v>
       </c>
-      <c r="B65" s="10">
+      <c r="B65" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>14796</v>
       </c>
@@ -6896,7 +6962,7 @@
       <c r="A66" t="s">
         <v>93</v>
       </c>
-      <c r="B66" s="10">
+      <c r="B66" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>29717</v>
       </c>
@@ -6917,7 +6983,7 @@
       <c r="A67" t="s">
         <v>94</v>
       </c>
-      <c r="B67" s="10">
+      <c r="B67" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>810</v>
       </c>
@@ -6938,7 +7004,7 @@
       <c r="A68" t="s">
         <v>95</v>
       </c>
-      <c r="B68" s="10">
+      <c r="B68" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>21787</v>
       </c>
@@ -6959,7 +7025,7 @@
       <c r="A69" t="s">
         <v>96</v>
       </c>
-      <c r="B69" s="10">
+      <c r="B69" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>9912</v>
       </c>
@@ -6980,7 +7046,7 @@
       <c r="A70" t="s">
         <v>97</v>
       </c>
-      <c r="B70" s="10">
+      <c r="B70" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>15505</v>
       </c>
@@ -7001,7 +7067,7 @@
       <c r="A71" t="s">
         <v>98</v>
       </c>
-      <c r="B71" s="10">
+      <c r="B71" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>10230</v>
       </c>
@@ -7022,7 +7088,7 @@
       <c r="A72" t="s">
         <v>99</v>
       </c>
-      <c r="B72" s="10">
+      <c r="B72" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>10231</v>
       </c>
@@ -7043,7 +7109,7 @@
       <c r="A73" t="s">
         <v>100</v>
       </c>
-      <c r="B73" s="10">
+      <c r="B73" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>30308</v>
       </c>
@@ -7064,7 +7130,7 @@
       <c r="A74" t="s">
         <v>101</v>
       </c>
-      <c r="B74" s="10">
+      <c r="B74" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>4301</v>
       </c>
@@ -7085,7 +7151,7 @@
       <c r="A75" t="s">
         <v>102</v>
       </c>
-      <c r="B75" s="10">
+      <c r="B75" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>19842</v>
       </c>
@@ -7106,7 +7172,7 @@
       <c r="A76" t="s">
         <v>103</v>
       </c>
-      <c r="B76" s="10">
+      <c r="B76" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>19603</v>
       </c>
@@ -7127,7 +7193,7 @@
       <c r="A77" t="s">
         <v>104</v>
       </c>
-      <c r="B77" s="10">
+      <c r="B77" s="5">
         <f t="shared" ref="B77:B140" ca="1" si="7">MOD(B76*F$11+F$12,F$13)</f>
         <v>5328</v>
       </c>
@@ -7148,7 +7214,7 @@
       <c r="A78" t="s">
         <v>105</v>
       </c>
-      <c r="B78" s="10">
+      <c r="B78" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>27849</v>
       </c>
@@ -7169,7 +7235,7 @@
       <c r="A79" t="s">
         <v>106</v>
       </c>
-      <c r="B79" s="10">
+      <c r="B79" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>16334</v>
       </c>
@@ -7190,7 +7256,7 @@
       <c r="A80" t="s">
         <v>107</v>
       </c>
-      <c r="B80" s="10">
+      <c r="B80" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>7919</v>
       </c>
@@ -7211,7 +7277,7 @@
       <c r="A81" t="s">
         <v>108</v>
       </c>
-      <c r="B81" s="10">
+      <c r="B81" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>11772</v>
       </c>
@@ -7232,7 +7298,7 @@
       <c r="A82" t="s">
         <v>109</v>
       </c>
-      <c r="B82" s="10">
+      <c r="B82" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>3205</v>
       </c>
@@ -7253,7 +7319,7 @@
       <c r="A83" t="s">
         <v>110</v>
       </c>
-      <c r="B83" s="10">
+      <c r="B83" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>2778</v>
       </c>
@@ -7274,7 +7340,7 @@
       <c r="A84" t="s">
         <v>111</v>
       </c>
-      <c r="B84" s="10">
+      <c r="B84" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>15115</v>
       </c>
@@ -7295,7 +7361,7 @@
       <c r="A85" t="s">
         <v>112</v>
       </c>
-      <c r="B85" s="10">
+      <c r="B85" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>11752</v>
       </c>
@@ -7316,7 +7382,7 @@
       <c r="A86" t="s">
         <v>113</v>
       </c>
-      <c r="B86" s="10">
+      <c r="B86" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>27649</v>
       </c>
@@ -7337,7 +7403,7 @@
       <c r="A87" t="s">
         <v>114</v>
       </c>
-      <c r="B87" s="10">
+      <c r="B87" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>31398</v>
       </c>
@@ -7358,7 +7424,7 @@
       <c r="A88" t="s">
         <v>115</v>
       </c>
-      <c r="B88" s="10">
+      <c r="B88" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>31975</v>
       </c>
@@ -7379,7 +7445,7 @@
       <c r="A89" t="s">
         <v>116</v>
       </c>
-      <c r="B89" s="10">
+      <c r="B89" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>16532</v>
       </c>
@@ -7400,7 +7466,7 @@
       <c r="A90" t="s">
         <v>117</v>
       </c>
-      <c r="B90" s="10">
+      <c r="B90" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>18237</v>
       </c>
@@ -7421,7 +7487,7 @@
       <c r="A91" t="s">
         <v>118</v>
       </c>
-      <c r="B91" s="10">
+      <c r="B91" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>6962</v>
       </c>
@@ -7442,7 +7508,7 @@
       <c r="A92" t="s">
         <v>119</v>
       </c>
-      <c r="B92" s="10">
+      <c r="B92" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>131</v>
       </c>
@@ -7463,7 +7529,7 @@
       <c r="A93" t="s">
         <v>120</v>
       </c>
-      <c r="B93" s="10">
+      <c r="B93" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>20992</v>
       </c>
@@ -7484,7 +7550,7 @@
       <c r="A94" t="s">
         <v>121</v>
       </c>
-      <c r="B94" s="10">
+      <c r="B94" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>6713</v>
       </c>
@@ -7505,7 +7571,7 @@
       <c r="A95" t="s">
         <v>122</v>
       </c>
-      <c r="B95" s="10">
+      <c r="B95" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>14462</v>
       </c>
@@ -7526,7 +7592,7 @@
       <c r="A96" t="s">
         <v>123</v>
       </c>
-      <c r="B96" s="10">
+      <c r="B96" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>8671</v>
       </c>
@@ -7547,7 +7613,7 @@
       <c r="A97" t="s">
         <v>124</v>
       </c>
-      <c r="B97" s="10">
+      <c r="B97" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>3628</v>
       </c>
@@ -7568,7 +7634,7 @@
       <c r="A98" t="s">
         <v>125</v>
       </c>
-      <c r="B98" s="10">
+      <c r="B98" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>8437</v>
       </c>
@@ -7589,7 +7655,7 @@
       <c r="A99" t="s">
         <v>126</v>
       </c>
-      <c r="B99" s="10">
+      <c r="B99" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>24202</v>
       </c>
@@ -7610,7 +7676,7 @@
       <c r="A100" t="s">
         <v>127</v>
       </c>
-      <c r="B100" s="10">
+      <c r="B100" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>31995</v>
       </c>
@@ -7631,7 +7697,7 @@
       <c r="A101" t="s">
         <v>128</v>
       </c>
-      <c r="B101" s="10">
+      <c r="B101" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>24856</v>
       </c>
@@ -7652,7 +7718,7 @@
       <c r="A102" t="s">
         <v>129</v>
       </c>
-      <c r="B102" s="10">
+      <c r="B102" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>22385</v>
       </c>
@@ -7673,7 +7739,7 @@
       <c r="A103" t="s">
         <v>130</v>
       </c>
-      <c r="B103" s="10">
+      <c r="B103" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>22870</v>
       </c>
@@ -7694,7 +7760,7 @@
       <c r="A104" t="s">
         <v>131</v>
       </c>
-      <c r="B104" s="10">
+      <c r="B104" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>28119</v>
       </c>
@@ -7715,7 +7781,7 @@
       <c r="A105" t="s">
         <v>132</v>
       </c>
-      <c r="B105" s="10">
+      <c r="B105" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>30404</v>
       </c>
@@ -7736,7 +7802,7 @@
       <c r="A106" t="s">
         <v>133</v>
       </c>
-      <c r="B106" s="10">
+      <c r="B106" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>31149</v>
       </c>
@@ -7757,7 +7823,7 @@
       <c r="A107" t="s">
         <v>134</v>
       </c>
-      <c r="B107" s="10">
+      <c r="B107" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>13538</v>
       </c>
@@ -7778,7 +7844,7 @@
       <c r="A108" t="s">
         <v>135</v>
       </c>
-      <c r="B108" s="10">
+      <c r="B108" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>4211</v>
       </c>
@@ -7799,7 +7865,7 @@
       <c r="A109" t="s">
         <v>136</v>
       </c>
-      <c r="B109" s="10">
+      <c r="B109" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>15152</v>
       </c>
@@ -7820,7 +7886,7 @@
       <c r="A110" t="s">
         <v>137</v>
       </c>
-      <c r="B110" s="10">
+      <c r="B110" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>937</v>
       </c>
@@ -7841,7 +7907,7 @@
       <c r="A111" t="s">
         <v>138</v>
       </c>
-      <c r="B111" s="10">
+      <c r="B111" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>15662</v>
       </c>
@@ -7862,7 +7928,7 @@
       <c r="A112" t="s">
         <v>139</v>
       </c>
-      <c r="B112" s="10">
+      <c r="B112" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>16591</v>
       </c>
@@ -7883,7 +7949,7 @@
       <c r="A113" t="s">
         <v>140</v>
       </c>
-      <c r="B113" s="10">
+      <c r="B113" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>23132</v>
       </c>
@@ -7904,7 +7970,7 @@
       <c r="A114" t="s">
         <v>141</v>
       </c>
-      <c r="B114" s="10">
+      <c r="B114" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>12645</v>
       </c>
@@ -7925,7 +7991,7 @@
       <c r="A115" t="s">
         <v>142</v>
       </c>
-      <c r="B115" s="10">
+      <c r="B115" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>32314</v>
       </c>
@@ -7946,7 +8012,7 @@
       <c r="A116" t="s">
         <v>143</v>
       </c>
-      <c r="B116" s="10">
+      <c r="B116" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>6891</v>
       </c>
@@ -7967,7 +8033,7 @@
       <c r="A117" t="s">
         <v>144</v>
       </c>
-      <c r="B117" s="10">
+      <c r="B117" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>16456</v>
       </c>
@@ -7988,7 +8054,7 @@
       <c r="A118" t="s">
         <v>145</v>
       </c>
-      <c r="B118" s="10">
+      <c r="B118" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>32481</v>
       </c>
@@ -8009,7 +8075,7 @@
       <c r="A119" t="s">
         <v>146</v>
       </c>
-      <c r="B119" s="10">
+      <c r="B119" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>17414</v>
       </c>
@@ -8030,7 +8096,7 @@
       <c r="A120" t="s">
         <v>147</v>
       </c>
-      <c r="B120" s="10">
+      <c r="B120" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>31431</v>
       </c>
@@ -8051,7 +8117,7 @@
       <c r="A121" t="s">
         <v>148</v>
       </c>
-      <c r="B121" s="10">
+      <c r="B121" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>6388</v>
       </c>
@@ -8072,7 +8138,7 @@
       <c r="A122" t="s">
         <v>149</v>
       </c>
-      <c r="B122" s="10">
+      <c r="B122" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>10269</v>
       </c>
@@ -8093,7 +8159,7 @@
       <c r="A123" t="s">
         <v>150</v>
       </c>
-      <c r="B123" s="10">
+      <c r="B123" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>6802</v>
       </c>
@@ -8114,7 +8180,7 @@
       <c r="A124" t="s">
         <v>151</v>
       </c>
-      <c r="B124" s="10">
+      <c r="B124" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>31843</v>
       </c>
@@ -8135,7 +8201,7 @@
       <c r="A125" t="s">
         <v>152</v>
       </c>
-      <c r="B125" s="10">
+      <c r="B125" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>20576</v>
       </c>
@@ -8156,7 +8222,7 @@
       <c r="A126" t="s">
         <v>153</v>
       </c>
-      <c r="B126" s="10">
+      <c r="B126" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>10521</v>
       </c>
@@ -8177,7 +8243,7 @@
       <c r="A127" t="s">
         <v>154</v>
       </c>
-      <c r="B127" s="10">
+      <c r="B127" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>19934</v>
       </c>
@@ -8198,7 +8264,7 @@
       <c r="A128" t="s">
         <v>155</v>
       </c>
-      <c r="B128" s="10">
+      <c r="B128" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>31679</v>
       </c>
@@ -8219,7 +8285,7 @@
       <c r="A129" t="s">
         <v>156</v>
       </c>
-      <c r="B129" s="10">
+      <c r="B129" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>4748</v>
       </c>
@@ -8240,7 +8306,7 @@
       <c r="A130" t="s">
         <v>157</v>
       </c>
-      <c r="B130" s="10">
+      <c r="B130" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>15829</v>
       </c>
@@ -8261,7 +8327,7 @@
       <c r="A131" t="s">
         <v>158</v>
       </c>
-      <c r="B131" s="10">
+      <c r="B131" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>27114</v>
       </c>
@@ -8282,7 +8348,7 @@
       <c r="A132" t="s">
         <v>159</v>
       </c>
-      <c r="B132" s="10">
+      <c r="B132" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>5339</v>
       </c>
@@ -8303,7 +8369,7 @@
       <c r="A133" t="s">
         <v>160</v>
       </c>
-      <c r="B133" s="10">
+      <c r="B133" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>19320</v>
       </c>
@@ -8324,7 +8390,7 @@
       <c r="A134" t="s">
         <v>161</v>
       </c>
-      <c r="B134" s="10">
+      <c r="B134" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>25169</v>
       </c>
@@ -8345,7 +8411,7 @@
       <c r="A135" t="s">
         <v>162</v>
       </c>
-      <c r="B135" s="10">
+      <c r="B135" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>15030</v>
       </c>
@@ -8366,7 +8432,7 @@
       <c r="A136" t="s">
         <v>163</v>
       </c>
-      <c r="B136" s="10">
+      <c r="B136" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>9143</v>
       </c>
@@ -8387,7 +8453,7 @@
       <c r="A137" t="s">
         <v>164</v>
       </c>
-      <c r="B137" s="10">
+      <c r="B137" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>10020</v>
       </c>
@@ -8408,7 +8474,7 @@
       <c r="A138" t="s">
         <v>165</v>
       </c>
-      <c r="B138" s="10">
+      <c r="B138" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>21133</v>
       </c>
@@ -8429,7 +8495,7 @@
       <c r="A139" t="s">
         <v>166</v>
       </c>
-      <c r="B139" s="10">
+      <c r="B139" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>19522</v>
       </c>
@@ -8450,7 +8516,7 @@
       <c r="A140" t="s">
         <v>167</v>
       </c>
-      <c r="B140" s="10">
+      <c r="B140" s="5">
         <f t="shared" ca="1" si="7"/>
         <v>17491</v>
       </c>
@@ -8471,7 +8537,7 @@
       <c r="A141" t="s">
         <v>168</v>
       </c>
-      <c r="B141" s="10">
+      <c r="B141" s="5">
         <f t="shared" ref="B141:B204" ca="1" si="11">MOD(B140*F$11+F$12,F$13)</f>
         <v>4496</v>
       </c>
@@ -8492,7 +8558,7 @@
       <c r="A142" t="s">
         <v>169</v>
       </c>
-      <c r="B142" s="10">
+      <c r="B142" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>2697</v>
       </c>
@@ -8513,7 +8579,7 @@
       <c r="A143" t="s">
         <v>170</v>
       </c>
-      <c r="B143" s="10">
+      <c r="B143" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>27278</v>
       </c>
@@ -8534,7 +8600,7 @@
       <c r="A144" t="s">
         <v>171</v>
       </c>
-      <c r="B144" s="10">
+      <c r="B144" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>21167</v>
       </c>
@@ -8555,7 +8621,7 @@
       <c r="A145" t="s">
         <v>172</v>
       </c>
-      <c r="B145" s="10">
+      <c r="B145" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>14012</v>
       </c>
@@ -8576,7 +8642,7 @@
       <c r="A146" t="s">
         <v>173</v>
       </c>
-      <c r="B146" s="10">
+      <c r="B146" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>17989</v>
       </c>
@@ -8597,7 +8663,7 @@
       <c r="A147" t="s">
         <v>174</v>
       </c>
-      <c r="B147" s="10">
+      <c r="B147" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>8602</v>
       </c>
@@ -8618,7 +8684,7 @@
       <c r="A148" t="s">
         <v>175</v>
       </c>
-      <c r="B148" s="10">
+      <c r="B148" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>27339</v>
       </c>
@@ -8639,7 +8705,7 @@
       <c r="A149" t="s">
         <v>176</v>
       </c>
-      <c r="B149" s="10">
+      <c r="B149" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>680</v>
       </c>
@@ -8660,7 +8726,7 @@
       <c r="A150" t="s">
         <v>177</v>
       </c>
-      <c r="B150" s="10">
+      <c r="B150" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>449</v>
       </c>
@@ -8681,7 +8747,7 @@
       <c r="A151" t="s">
         <v>178</v>
       </c>
-      <c r="B151" s="10">
+      <c r="B151" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>15718</v>
       </c>
@@ -8702,7 +8768,7 @@
       <c r="A152" t="s">
         <v>179</v>
       </c>
-      <c r="B152" s="10">
+      <c r="B152" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>26791</v>
       </c>
@@ -8723,7 +8789,7 @@
       <c r="A153" t="s">
         <v>180</v>
       </c>
-      <c r="B153" s="10">
+      <c r="B153" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>8532</v>
       </c>
@@ -8744,7 +8810,7 @@
       <c r="A154" t="s">
         <v>181</v>
       </c>
-      <c r="B154" s="10">
+      <c r="B154" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>30973</v>
       </c>
@@ -8765,7 +8831,7 @@
       <c r="A155" t="s">
         <v>182</v>
       </c>
-      <c r="B155" s="10">
+      <c r="B155" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>18930</v>
       </c>
@@ -8786,7 +8852,7 @@
       <c r="A156" t="s">
         <v>183</v>
       </c>
-      <c r="B156" s="10">
+      <c r="B156" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>26691</v>
       </c>
@@ -8807,7 +8873,7 @@
       <c r="A157" t="s">
         <v>184</v>
       </c>
-      <c r="B157" s="10">
+      <c r="B157" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>32448</v>
       </c>
@@ -8828,7 +8894,7 @@
       <c r="A158" t="s">
         <v>185</v>
       </c>
-      <c r="B158" s="10">
+      <c r="B158" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>10233</v>
       </c>
@@ -8849,7 +8915,7 @@
       <c r="A159" t="s">
         <v>186</v>
       </c>
-      <c r="B159" s="10">
+      <c r="B159" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>4926</v>
       </c>
@@ -8870,7 +8936,7 @@
       <c r="A160" t="s">
         <v>187</v>
       </c>
-      <c r="B160" s="10">
+      <c r="B160" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>17823</v>
       </c>
@@ -8891,7 +8957,7 @@
       <c r="A161" t="s">
         <v>188</v>
       </c>
-      <c r="B161" s="10">
+      <c r="B161" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>18156</v>
       </c>
@@ -8912,7 +8978,7 @@
       <c r="A162" t="s">
         <v>189</v>
       </c>
-      <c r="B162" s="10">
+      <c r="B162" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>19125</v>
       </c>
@@ -8933,7 +8999,7 @@
       <c r="A163" t="s">
         <v>190</v>
       </c>
-      <c r="B163" s="10">
+      <c r="B163" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>9546</v>
       </c>
@@ -8954,7 +9020,7 @@
       <c r="A164" t="s">
         <v>191</v>
       </c>
-      <c r="B164" s="10">
+      <c r="B164" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>7355</v>
       </c>
@@ -8975,7 +9041,7 @@
       <c r="A165" t="s">
         <v>192</v>
       </c>
-      <c r="B165" s="10">
+      <c r="B165" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>26072</v>
       </c>
@@ -8996,7 +9062,7 @@
       <c r="A166" t="s">
         <v>193</v>
       </c>
-      <c r="B166" s="10">
+      <c r="B166" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>23857</v>
       </c>
@@ -9017,7 +9083,7 @@
       <c r="A167" t="s">
         <v>194</v>
       </c>
-      <c r="B167" s="10">
+      <c r="B167" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>19478</v>
       </c>
@@ -9038,7 +9104,7 @@
       <c r="A168" t="s">
         <v>195</v>
       </c>
-      <c r="B168" s="10">
+      <c r="B168" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>18839</v>
       </c>
@@ -9059,7 +9125,7 @@
       <c r="A169" t="s">
         <v>196</v>
       </c>
-      <c r="B169" s="10">
+      <c r="B169" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>1924</v>
       </c>
@@ -9080,7 +9146,7 @@
       <c r="A170" t="s">
         <v>197</v>
       </c>
-      <c r="B170" s="10">
+      <c r="B170" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>7021</v>
       </c>
@@ -9101,7 +9167,7 @@
       <c r="A171" t="s">
         <v>198</v>
       </c>
-      <c r="B171" s="10">
+      <c r="B171" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>5026</v>
       </c>
@@ -9122,7 +9188,7 @@
       <c r="A172" t="s">
         <v>199</v>
       </c>
-      <c r="B172" s="10">
+      <c r="B172" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>26675</v>
       </c>
@@ -9143,7 +9209,7 @@
       <c r="A173" t="s">
         <v>200</v>
       </c>
-      <c r="B173" s="10">
+      <c r="B173" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>6128</v>
       </c>
@@ -9164,7 +9230,7 @@
       <c r="A174" t="s">
         <v>201</v>
       </c>
-      <c r="B174" s="10">
+      <c r="B174" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>361</v>
       </c>
@@ -9185,7 +9251,7 @@
       <c r="A175" t="s">
         <v>202</v>
       </c>
-      <c r="B175" s="10">
+      <c r="B175" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>18414</v>
       </c>
@@ -9206,7 +9272,7 @@
       <c r="A176" t="s">
         <v>203</v>
       </c>
-      <c r="B176" s="10">
+      <c r="B176" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>21647</v>
       </c>
@@ -9227,7 +9293,7 @@
       <c r="A177" t="s">
         <v>204</v>
       </c>
-      <c r="B177" s="10">
+      <c r="B177" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>17180</v>
       </c>
@@ -9248,7 +9314,7 @@
       <c r="A178" t="s">
         <v>205</v>
       </c>
-      <c r="B178" s="10">
+      <c r="B178" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>19237</v>
       </c>
@@ -9269,7 +9335,7 @@
       <c r="A179" t="s">
         <v>206</v>
       </c>
-      <c r="B179" s="10">
+      <c r="B179" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>29946</v>
       </c>
@@ -9290,7 +9356,7 @@
       <c r="A180" t="s">
         <v>207</v>
       </c>
-      <c r="B180" s="10">
+      <c r="B180" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>10923</v>
       </c>
@@ -9311,7 +9377,7 @@
       <c r="A181" t="s">
         <v>208</v>
       </c>
-      <c r="B181" s="10">
+      <c r="B181" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>29960</v>
       </c>
@@ -9332,7 +9398,7 @@
       <c r="A182" t="s">
         <v>209</v>
       </c>
-      <c r="B182" s="10">
+      <c r="B182" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>29857</v>
       </c>
@@ -9353,7 +9419,7 @@
       <c r="A183" t="s">
         <v>210</v>
       </c>
-      <c r="B183" s="10">
+      <c r="B183" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>26310</v>
       </c>
@@ -9374,7 +9440,7 @@
       <c r="A184" t="s">
         <v>211</v>
       </c>
-      <c r="B184" s="10">
+      <c r="B184" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>18055</v>
       </c>
@@ -9395,7 +9461,7 @@
       <c r="A185" t="s">
         <v>212</v>
       </c>
-      <c r="B185" s="10">
+      <c r="B185" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>22964</v>
       </c>
@@ -9416,7 +9482,7 @@
       <c r="A186" t="s">
         <v>213</v>
       </c>
-      <c r="B186" s="10">
+      <c r="B186" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>14813</v>
       </c>
@@ -9437,7 +9503,7 @@
       <c r="A187" t="s">
         <v>214</v>
       </c>
-      <c r="B187" s="10">
+      <c r="B187" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>10578</v>
       </c>
@@ -9458,7 +9524,7 @@
       <c r="A188" t="s">
         <v>215</v>
       </c>
-      <c r="B188" s="10">
+      <c r="B188" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>17443</v>
       </c>
@@ -9479,7 +9545,7 @@
       <c r="A189" t="s">
         <v>216</v>
       </c>
-      <c r="B189" s="10">
+      <c r="B189" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>23840</v>
       </c>
@@ -9500,7 +9566,7 @@
       <c r="A190" t="s">
         <v>217</v>
       </c>
-      <c r="B190" s="10">
+      <c r="B190" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>5849</v>
       </c>
@@ -9521,7 +9587,7 @@
       <c r="A191" t="s">
         <v>218</v>
       </c>
-      <c r="B191" s="10">
+      <c r="B191" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>2206</v>
       </c>
@@ -9542,7 +9608,7 @@
       <c r="A192" t="s">
         <v>219</v>
       </c>
-      <c r="B192" s="10">
+      <c r="B192" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>32639</v>
       </c>
@@ -9563,7 +9629,7 @@
       <c r="A193" t="s">
         <v>220</v>
       </c>
-      <c r="B193" s="10">
+      <c r="B193" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>11084</v>
       </c>
@@ -9584,7 +9650,7 @@
       <c r="A194" t="s">
         <v>221</v>
       </c>
-      <c r="B194" s="10">
+      <c r="B194" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>18325</v>
       </c>
@@ -9605,7 +9671,7 @@
       <c r="A195" t="s">
         <v>222</v>
       </c>
-      <c r="B195" s="10">
+      <c r="B195" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>4266</v>
       </c>
@@ -9626,7 +9692,7 @@
       <c r="A196" t="s">
         <v>223</v>
       </c>
-      <c r="B196" s="10">
+      <c r="B196" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>5275</v>
       </c>
@@ -9647,7 +9713,7 @@
       <c r="A197" t="s">
         <v>224</v>
       </c>
-      <c r="B197" s="10">
+      <c r="B197" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>12344</v>
       </c>
@@ -9668,7 +9734,7 @@
       <c r="A198" t="s">
         <v>225</v>
       </c>
-      <c r="B198" s="10">
+      <c r="B198" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>18449</v>
       </c>
@@ -9689,7 +9755,7 @@
       <c r="A199" t="s">
         <v>226</v>
       </c>
-      <c r="B199" s="10">
+      <c r="B199" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>3446</v>
       </c>
@@ -9710,7 +9776,7 @@
       <c r="A200" t="s">
         <v>227</v>
       </c>
-      <c r="B200" s="10">
+      <c r="B200" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>24439</v>
       </c>
@@ -9731,7 +9797,7 @@
       <c r="A201" t="s">
         <v>228</v>
       </c>
-      <c r="B201" s="10">
+      <c r="B201" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>6116</v>
       </c>
@@ -9752,7 +9818,7 @@
       <c r="A202" t="s">
         <v>229</v>
       </c>
-      <c r="B202" s="10">
+      <c r="B202" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>21581</v>
       </c>
@@ -9773,7 +9839,7 @@
       <c r="A203" t="s">
         <v>230</v>
       </c>
-      <c r="B203" s="10">
+      <c r="B203" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>2818</v>
       </c>
@@ -9794,7 +9860,7 @@
       <c r="A204" t="s">
         <v>231</v>
       </c>
-      <c r="B204" s="10">
+      <c r="B204" s="5">
         <f t="shared" ca="1" si="11"/>
         <v>31763</v>
       </c>
@@ -9815,7 +9881,7 @@
       <c r="A205" t="s">
         <v>232</v>
       </c>
-      <c r="B205" s="10">
+      <c r="B205" s="5">
         <f t="shared" ref="B205:B268" ca="1" si="15">MOD(B204*F$11+F$12,F$13)</f>
         <v>20048</v>
       </c>
@@ -9836,7 +9902,7 @@
       <c r="A206" t="s">
         <v>233</v>
       </c>
-      <c r="B206" s="10">
+      <c r="B206" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>26697</v>
       </c>
@@ -9857,7 +9923,7 @@
       <c r="A207" t="s">
         <v>234</v>
       </c>
-      <c r="B207" s="10">
+      <c r="B207" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>21838</v>
       </c>
@@ -9878,7 +9944,7 @@
       <c r="A208" t="s">
         <v>235</v>
       </c>
-      <c r="B208" s="10">
+      <c r="B208" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>18031</v>
       </c>
@@ -9899,7 +9965,7 @@
       <c r="A209" t="s">
         <v>236</v>
       </c>
-      <c r="B209" s="10">
+      <c r="B209" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>32636</v>
       </c>
@@ -9920,7 +9986,7 @@
       <c r="A210" t="s">
         <v>237</v>
       </c>
-      <c r="B210" s="10">
+      <c r="B210" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>16389</v>
       </c>
@@ -9941,7 +10007,7 @@
       <c r="A211" t="s">
         <v>238</v>
       </c>
-      <c r="B211" s="10">
+      <c r="B211" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>30810</v>
       </c>
@@ -9962,7 +10028,7 @@
       <c r="A212" t="s">
         <v>239</v>
       </c>
-      <c r="B212" s="10">
+      <c r="B212" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>23179</v>
       </c>
@@ -9983,7 +10049,7 @@
       <c r="A213" t="s">
         <v>240</v>
       </c>
-      <c r="B213" s="10">
+      <c r="B213" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>5992</v>
       </c>
@@ -10004,7 +10070,7 @@
       <c r="A214" t="s">
         <v>241</v>
       </c>
-      <c r="B214" s="10">
+      <c r="B214" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>22401</v>
       </c>
@@ -10025,7 +10091,7 @@
       <c r="A215" t="s">
         <v>242</v>
       </c>
-      <c r="B215" s="10">
+      <c r="B215" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>16422</v>
       </c>
@@ -10046,7 +10112,7 @@
       <c r="A216" t="s">
         <v>243</v>
       </c>
-      <c r="B216" s="10">
+      <c r="B216" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>5223</v>
       </c>
@@ -10067,7 +10133,7 @@
       <c r="A217" t="s">
         <v>244</v>
       </c>
-      <c r="B217" s="10">
+      <c r="B217" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>16916</v>
       </c>
@@ -10088,7 +10154,7 @@
       <c r="A218" t="s">
         <v>245</v>
       </c>
-      <c r="B218" s="10">
+      <c r="B218" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>27325</v>
       </c>
@@ -10109,7 +10175,7 @@
       <c r="A219" t="s">
         <v>246</v>
       </c>
-      <c r="B219" s="10">
+      <c r="B219" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>14514</v>
       </c>
@@ -10130,7 +10196,7 @@
       <c r="A220" t="s">
         <v>247</v>
       </c>
-      <c r="B220" s="10">
+      <c r="B220" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>4099</v>
       </c>
@@ -10151,7 +10217,7 @@
       <c r="A221" t="s">
         <v>248</v>
       </c>
-      <c r="B221" s="10">
+      <c r="B221" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>27520</v>
       </c>
@@ -10172,7 +10238,7 @@
       <c r="A222" t="s">
         <v>249</v>
       </c>
-      <c r="B222" s="10">
+      <c r="B222" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>30137</v>
       </c>
@@ -10193,7 +10259,7 @@
       <c r="A223" t="s">
         <v>250</v>
       </c>
-      <c r="B223" s="10">
+      <c r="B223" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>11774</v>
       </c>
@@ -10214,7 +10280,7 @@
       <c r="A224" t="s">
         <v>251</v>
       </c>
-      <c r="B224" s="10">
+      <c r="B224" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>10591</v>
       </c>
@@ -10235,7 +10301,7 @@
       <c r="A225" t="s">
         <v>252</v>
       </c>
-      <c r="B225" s="10">
+      <c r="B225" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>16300</v>
       </c>
@@ -10256,7 +10322,7 @@
       <c r="A226" t="s">
         <v>253</v>
       </c>
-      <c r="B226" s="10">
+      <c r="B226" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>13429</v>
       </c>
@@ -10277,7 +10343,7 @@
       <c r="A227" t="s">
         <v>254</v>
       </c>
-      <c r="B227" s="10">
+      <c r="B227" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>11274</v>
       </c>
@@ -10298,7 +10364,7 @@
       <c r="A228" t="s">
         <v>255</v>
       </c>
-      <c r="B228" s="10">
+      <c r="B228" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>31867</v>
       </c>
@@ -10319,7 +10385,7 @@
       <c r="A229" t="s">
         <v>256</v>
       </c>
-      <c r="B229" s="10">
+      <c r="B229" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>10904</v>
       </c>
@@ -10340,7 +10406,7 @@
       <c r="A230" t="s">
         <v>257</v>
       </c>
-      <c r="B230" s="10">
+      <c r="B230" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>8945</v>
       </c>
@@ -10361,7 +10427,7 @@
       <c r="A231" t="s">
         <v>258</v>
       </c>
-      <c r="B231" s="10">
+      <c r="B231" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>32470</v>
       </c>
@@ -10382,7 +10448,7 @@
       <c r="A232" t="s">
         <v>259</v>
       </c>
-      <c r="B232" s="10">
+      <c r="B232" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>25943</v>
       </c>
@@ -10403,7 +10469,7 @@
       <c r="A233" t="s">
         <v>260</v>
       </c>
-      <c r="B233" s="10">
+      <c r="B233" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>22596</v>
       </c>
@@ -10424,7 +10490,7 @@
       <c r="A234" t="s">
         <v>261</v>
       </c>
-      <c r="B234" s="10">
+      <c r="B234" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>32045</v>
       </c>
@@ -10445,7 +10511,7 @@
       <c r="A235" t="s">
         <v>262</v>
       </c>
-      <c r="B235" s="10">
+      <c r="B235" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>12898</v>
       </c>
@@ -10466,7 +10532,7 @@
       <c r="A236" t="s">
         <v>263</v>
       </c>
-      <c r="B236" s="10">
+      <c r="B236" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>32755</v>
       </c>
@@ -10487,7 +10553,7 @@
       <c r="A237" t="s">
         <v>264</v>
       </c>
-      <c r="B237" s="10">
+      <c r="B237" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>13488</v>
       </c>
@@ -10508,7 +10574,7 @@
       <c r="A238" t="s">
         <v>265</v>
       </c>
-      <c r="B238" s="10">
+      <c r="B238" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>16169</v>
       </c>
@@ -10529,7 +10595,7 @@
       <c r="A239" t="s">
         <v>266</v>
       </c>
-      <c r="B239" s="10">
+      <c r="B239" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>4782</v>
       </c>
@@ -10550,7 +10616,7 @@
       <c r="A240" t="s">
         <v>267</v>
       </c>
-      <c r="B240" s="10">
+      <c r="B240" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>10319</v>
       </c>
@@ -10571,7 +10637,7 @@
       <c r="A241" t="s">
         <v>268</v>
       </c>
-      <c r="B241" s="10">
+      <c r="B241" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>27612</v>
       </c>
@@ -10592,7 +10658,7 @@
       <c r="A242" t="s">
         <v>269</v>
       </c>
-      <c r="B242" s="10">
+      <c r="B242" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>9445</v>
       </c>
@@ -10613,7 +10679,7 @@
       <c r="A243" t="s">
         <v>270</v>
       </c>
-      <c r="B243" s="10">
+      <c r="B243" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>11194</v>
       </c>
@@ -10634,7 +10700,7 @@
       <c r="A244" t="s">
         <v>271</v>
       </c>
-      <c r="B244" s="10">
+      <c r="B244" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>31339</v>
       </c>
@@ -10655,7 +10721,7 @@
       <c r="A245" t="s">
         <v>272</v>
       </c>
-      <c r="B245" s="10">
+      <c r="B245" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>27080</v>
       </c>
@@ -10676,7 +10742,7 @@
       <c r="A246" t="s">
         <v>273</v>
       </c>
-      <c r="B246" s="10">
+      <c r="B246" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>10849</v>
       </c>
@@ -10697,7 +10763,7 @@
       <c r="A247" t="s">
         <v>274</v>
       </c>
-      <c r="B247" s="10">
+      <c r="B247" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>18822</v>
       </c>
@@ -10718,7 +10784,7 @@
       <c r="A248" t="s">
         <v>275</v>
       </c>
-      <c r="B248" s="10">
+      <c r="B248" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>21063</v>
       </c>
@@ -10739,7 +10805,7 @@
       <c r="A249" t="s">
         <v>276</v>
       </c>
-      <c r="B249" s="10">
+      <c r="B249" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>23156</v>
       </c>
@@ -10760,7 +10826,7 @@
       <c r="A250" t="s">
         <v>277</v>
       </c>
-      <c r="B250" s="10">
+      <c r="B250" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>2973</v>
       </c>
@@ -10781,7 +10847,7 @@
       <c r="A251" t="s">
         <v>278</v>
       </c>
-      <c r="B251" s="10">
+      <c r="B251" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>30738</v>
       </c>
@@ -10802,7 +10868,7 @@
       <c r="A252" t="s">
         <v>279</v>
       </c>
-      <c r="B252" s="10">
+      <c r="B252" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>19427</v>
       </c>
@@ -10823,7 +10889,7 @@
       <c r="A253" t="s">
         <v>280</v>
       </c>
-      <c r="B253" s="10">
+      <c r="B253" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>10720</v>
       </c>
@@ -10844,7 +10910,7 @@
       <c r="A254" t="s">
         <v>281</v>
       </c>
-      <c r="B254" s="10">
+      <c r="B254" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>17561</v>
       </c>
@@ -10865,7 +10931,7 @@
       <c r="A255" t="s">
         <v>282</v>
       </c>
-      <c r="B255" s="10">
+      <c r="B255" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>862</v>
       </c>
@@ -10886,7 +10952,7 @@
       <c r="A256" t="s">
         <v>283</v>
       </c>
-      <c r="B256" s="10">
+      <c r="B256" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>17215</v>
       </c>
@@ -10907,7 +10973,7 @@
       <c r="A257" t="s">
         <v>284</v>
       </c>
-      <c r="B257" s="10">
+      <c r="B257" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>1036</v>
       </c>
@@ -10928,7 +10994,7 @@
       <c r="A258" t="s">
         <v>285</v>
       </c>
-      <c r="B258" s="10">
+      <c r="B258" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>4437</v>
       </c>
@@ -10949,7 +11015,7 @@
       <c r="A259" t="s">
         <v>286</v>
       </c>
-      <c r="B259" s="10">
+      <c r="B259" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>30570</v>
       </c>
@@ -10970,7 +11036,7 @@
       <c r="A260" t="s">
         <v>287</v>
       </c>
-      <c r="B260" s="10">
+      <c r="B260" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>21595</v>
       </c>
@@ -10991,7 +11057,7 @@
       <c r="A261" t="s">
         <v>288</v>
       </c>
-      <c r="B261" s="10">
+      <c r="B261" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>21752</v>
       </c>
@@ -11012,7 +11078,7 @@
       <c r="A262" t="s">
         <v>289</v>
       </c>
-      <c r="B262" s="10">
+      <c r="B262" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>28113</v>
       </c>
@@ -11033,7 +11099,7 @@
       <c r="A263" t="s">
         <v>290</v>
       </c>
-      <c r="B263" s="10">
+      <c r="B263" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>8246</v>
       </c>
@@ -11054,7 +11120,7 @@
       <c r="A264" t="s">
         <v>291</v>
       </c>
-      <c r="B264" s="10">
+      <c r="B264" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>23351</v>
       </c>
@@ -11075,7 +11141,7 @@
       <c r="A265" t="s">
         <v>292</v>
       </c>
-      <c r="B265" s="10">
+      <c r="B265" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>18596</v>
       </c>
@@ -11096,7 +11162,7 @@
       <c r="A266" t="s">
         <v>293</v>
       </c>
-      <c r="B266" s="10">
+      <c r="B266" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>5645</v>
       </c>
@@ -11117,7 +11183,7 @@
       <c r="A267" t="s">
         <v>294</v>
       </c>
-      <c r="B267" s="10">
+      <c r="B267" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>2498</v>
       </c>
@@ -11138,7 +11204,7 @@
       <c r="A268" t="s">
         <v>295</v>
       </c>
-      <c r="B268" s="10">
+      <c r="B268" s="5">
         <f t="shared" ca="1" si="15"/>
         <v>29651</v>
       </c>
@@ -11159,7 +11225,7 @@
       <c r="A269" t="s">
         <v>296</v>
       </c>
-      <c r="B269" s="10">
+      <c r="B269" s="5">
         <f t="shared" ref="B269:B332" ca="1" si="19">MOD(B268*F$11+F$12,F$13)</f>
         <v>19216</v>
       </c>
@@ -11180,7 +11246,7 @@
       <c r="A270" t="s">
         <v>297</v>
       </c>
-      <c r="B270" s="10">
+      <c r="B270" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>1545</v>
       </c>
@@ -11201,7 +11267,7 @@
       <c r="A271" t="s">
         <v>298</v>
       </c>
-      <c r="B271" s="10">
+      <c r="B271" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>14</v>
       </c>
@@ -11222,7 +11288,7 @@
       <c r="A272" t="s">
         <v>299</v>
       </c>
-      <c r="B272" s="10">
+      <c r="B272" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>31279</v>
       </c>
@@ -11243,7 +11309,7 @@
       <c r="A273" t="s">
         <v>300</v>
       </c>
-      <c r="B273" s="10">
+      <c r="B273" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>2108</v>
       </c>
@@ -11264,7 +11330,7 @@
       <c r="A274" t="s">
         <v>301</v>
       </c>
-      <c r="B274" s="10">
+      <c r="B274" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>31173</v>
       </c>
@@ -11285,7 +11351,7 @@
       <c r="A275" t="s">
         <v>302</v>
       </c>
-      <c r="B275" s="10">
+      <c r="B275" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>3866</v>
       </c>
@@ -11306,7 +11372,7 @@
       <c r="A276" t="s">
         <v>303</v>
       </c>
-      <c r="B276" s="10">
+      <c r="B276" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>2635</v>
       </c>
@@ -11327,7 +11393,7 @@
       <c r="A277" t="s">
         <v>304</v>
       </c>
-      <c r="B277" s="10">
+      <c r="B277" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>27688</v>
       </c>
@@ -11348,7 +11414,7 @@
       <c r="A278" t="s">
         <v>305</v>
       </c>
-      <c r="B278" s="10">
+      <c r="B278" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>27969</v>
       </c>
@@ -11369,7 +11435,7 @@
       <c r="A279" t="s">
         <v>306</v>
       </c>
-      <c r="B279" s="10">
+      <c r="B279" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>742</v>
       </c>
@@ -11390,7 +11456,7 @@
       <c r="A280" t="s">
         <v>307</v>
       </c>
-      <c r="B280" s="10">
+      <c r="B280" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>39</v>
       </c>
@@ -11411,7 +11477,7 @@
       <c r="A281" t="s">
         <v>308</v>
       </c>
-      <c r="B281" s="10">
+      <c r="B281" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>8916</v>
       </c>
@@ -11432,7 +11498,7 @@
       <c r="A282" t="s">
         <v>309</v>
       </c>
-      <c r="B282" s="10">
+      <c r="B282" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>7293</v>
       </c>
@@ -11453,7 +11519,7 @@
       <c r="A283" t="s">
         <v>310</v>
       </c>
-      <c r="B283" s="10">
+      <c r="B283" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>26482</v>
       </c>
@@ -11474,7 +11540,7 @@
       <c r="A284" t="s">
         <v>311</v>
       </c>
-      <c r="B284" s="10">
+      <c r="B284" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>30659</v>
       </c>
@@ -11495,7 +11561,7 @@
       <c r="A285" t="s">
         <v>312</v>
       </c>
-      <c r="B285" s="10">
+      <c r="B285" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>6208</v>
       </c>
@@ -11516,7 +11582,7 @@
       <c r="A286" t="s">
         <v>313</v>
       </c>
-      <c r="B286" s="10">
+      <c r="B286" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>889</v>
       </c>
@@ -11537,7 +11603,7 @@
       <c r="A287" t="s">
         <v>314</v>
       </c>
-      <c r="B287" s="10">
+      <c r="B287" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>2238</v>
       </c>
@@ -11558,7 +11624,7 @@
       <c r="A288" t="s">
         <v>315</v>
       </c>
-      <c r="B288" s="10">
+      <c r="B288" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>19743</v>
       </c>
@@ -11579,7 +11645,7 @@
       <c r="A289" t="s">
         <v>316</v>
       </c>
-      <c r="B289" s="10">
+      <c r="B289" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>30828</v>
       </c>
@@ -11600,7 +11666,7 @@
       <c r="A290" t="s">
         <v>317</v>
       </c>
-      <c r="B290" s="10">
+      <c r="B290" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>24117</v>
       </c>
@@ -11621,7 +11687,7 @@
       <c r="A291" t="s">
         <v>318</v>
       </c>
-      <c r="B291" s="10">
+      <c r="B291" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>29386</v>
       </c>
@@ -11642,7 +11708,7 @@
       <c r="A292" t="s">
         <v>319</v>
       </c>
-      <c r="B292" s="10">
+      <c r="B292" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>7227</v>
       </c>
@@ -11663,7 +11729,7 @@
       <c r="A293" t="s">
         <v>320</v>
       </c>
-      <c r="B293" s="10">
+      <c r="B293" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>12120</v>
       </c>
@@ -11684,7 +11750,7 @@
       <c r="A294" t="s">
         <v>321</v>
       </c>
-      <c r="B294" s="10">
+      <c r="B294" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>10417</v>
       </c>
@@ -11705,7 +11771,7 @@
       <c r="A295" t="s">
         <v>322</v>
       </c>
-      <c r="B295" s="10">
+      <c r="B295" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>29078</v>
       </c>
@@ -11726,7 +11792,7 @@
       <c r="A296" t="s">
         <v>323</v>
       </c>
-      <c r="B296" s="10">
+      <c r="B296" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>16663</v>
       </c>
@@ -11747,7 +11813,7 @@
       <c r="A297" t="s">
         <v>324</v>
       </c>
-      <c r="B297" s="10">
+      <c r="B297" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>26884</v>
       </c>
@@ -11768,7 +11834,7 @@
       <c r="A298" t="s">
         <v>325</v>
       </c>
-      <c r="B298" s="10">
+      <c r="B298" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>7917</v>
       </c>
@@ -11789,7 +11855,7 @@
       <c r="A299" t="s">
         <v>326</v>
       </c>
-      <c r="B299" s="10">
+      <c r="B299" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>4386</v>
       </c>
@@ -11810,7 +11876,7 @@
       <c r="A300" t="s">
         <v>327</v>
       </c>
-      <c r="B300" s="10">
+      <c r="B300" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>22451</v>
       </c>
@@ -11831,7 +11897,7 @@
       <c r="A301" t="s">
         <v>328</v>
       </c>
-      <c r="B301" s="10">
+      <c r="B301" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>4464</v>
       </c>
@@ -11852,7 +11918,7 @@
       <c r="A302" t="s">
         <v>329</v>
       </c>
-      <c r="B302" s="10">
+      <c r="B302" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>15593</v>
       </c>
@@ -11873,7 +11939,7 @@
       <c r="A303" t="s">
         <v>330</v>
       </c>
-      <c r="B303" s="10">
+      <c r="B303" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>7534</v>
       </c>
@@ -11894,7 +11960,7 @@
       <c r="A304" t="s">
         <v>331</v>
       </c>
-      <c r="B304" s="10">
+      <c r="B304" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>15375</v>
       </c>
@@ -11915,7 +11981,7 @@
       <c r="A305" t="s">
         <v>332</v>
       </c>
-      <c r="B305" s="10">
+      <c r="B305" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>21660</v>
       </c>
@@ -11936,7 +12002,7 @@
       <c r="A306" t="s">
         <v>333</v>
       </c>
-      <c r="B306" s="10">
+      <c r="B306" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>16037</v>
       </c>
@@ -11957,7 +12023,7 @@
       <c r="A307" t="s">
         <v>334</v>
       </c>
-      <c r="B307" s="10">
+      <c r="B307" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>8826</v>
       </c>
@@ -11978,7 +12044,7 @@
       <c r="A308" t="s">
         <v>335</v>
       </c>
-      <c r="B308" s="10">
+      <c r="B308" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>2603</v>
       </c>
@@ -11999,7 +12065,7 @@
       <c r="A309" t="s">
         <v>336</v>
       </c>
-      <c r="B309" s="10">
+      <c r="B309" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>7816</v>
       </c>
@@ -12020,7 +12086,7 @@
       <c r="A310" t="s">
         <v>337</v>
       </c>
-      <c r="B310" s="10">
+      <c r="B310" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>8225</v>
       </c>
@@ -12041,7 +12107,7 @@
       <c r="A311" t="s">
         <v>338</v>
       </c>
-      <c r="B311" s="10">
+      <c r="B311" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>27718</v>
       </c>
@@ -12062,7 +12128,7 @@
       <c r="A312" t="s">
         <v>339</v>
       </c>
-      <c r="B312" s="10">
+      <c r="B312" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>7687</v>
       </c>
@@ -12083,7 +12149,7 @@
       <c r="A313" t="s">
         <v>340</v>
       </c>
-      <c r="B313" s="10">
+      <c r="B313" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>6964</v>
       </c>
@@ -12104,7 +12170,7 @@
       <c r="A314" t="s">
         <v>341</v>
       </c>
-      <c r="B314" s="10">
+      <c r="B314" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>7517</v>
       </c>
@@ -12125,7 +12191,7 @@
       <c r="A315" t="s">
         <v>342</v>
       </c>
-      <c r="B315" s="10">
+      <c r="B315" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>1746</v>
       </c>
@@ -12146,7 +12212,7 @@
       <c r="A316" t="s">
         <v>343</v>
       </c>
-      <c r="B316" s="10">
+      <c r="B316" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>5027</v>
       </c>
@@ -12167,7 +12233,7 @@
       <c r="A317" t="s">
         <v>344</v>
       </c>
-      <c r="B317" s="10">
+      <c r="B317" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>13984</v>
       </c>
@@ -12188,7 +12254,7 @@
       <c r="A318" t="s">
         <v>345</v>
       </c>
-      <c r="B318" s="10">
+      <c r="B318" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>12889</v>
       </c>
@@ -12209,7 +12275,7 @@
       <c r="A319" t="s">
         <v>346</v>
       </c>
-      <c r="B319" s="10">
+      <c r="B319" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>15902</v>
       </c>
@@ -12230,7 +12296,7 @@
       <c r="A320" t="s">
         <v>347</v>
       </c>
-      <c r="B320" s="10">
+      <c r="B320" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>18175</v>
       </c>
@@ -12251,7 +12317,7 @@
       <c r="A321" t="s">
         <v>348</v>
       </c>
-      <c r="B321" s="10">
+      <c r="B321" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>7372</v>
       </c>
@@ -12272,7 +12338,7 @@
       <c r="A322" t="s">
         <v>349</v>
       </c>
-      <c r="B322" s="10">
+      <c r="B322" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>6933</v>
       </c>
@@ -12293,7 +12359,7 @@
       <c r="A323" t="s">
         <v>350</v>
       </c>
-      <c r="B323" s="10">
+      <c r="B323" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>7722</v>
       </c>
@@ -12314,7 +12380,7 @@
       <c r="A324" t="s">
         <v>351</v>
       </c>
-      <c r="B324" s="10">
+      <c r="B324" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>21531</v>
       </c>
@@ -12335,7 +12401,7 @@
       <c r="A325" t="s">
         <v>352</v>
       </c>
-      <c r="B325" s="10">
+      <c r="B325" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>14776</v>
       </c>
@@ -12356,7 +12422,7 @@
       <c r="A326" t="s">
         <v>353</v>
       </c>
-      <c r="B326" s="10">
+      <c r="B326" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>21393</v>
       </c>
@@ -12377,7 +12443,7 @@
       <c r="A327" t="s">
         <v>354</v>
       </c>
-      <c r="B327" s="10">
+      <c r="B327" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>29430</v>
       </c>
@@ -12398,7 +12464,7 @@
       <c r="A328" t="s">
         <v>355</v>
       </c>
-      <c r="B328" s="10">
+      <c r="B328" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>5879</v>
       </c>
@@ -12419,7 +12485,7 @@
       <c r="A329" t="s">
         <v>356</v>
       </c>
-      <c r="B329" s="10">
+      <c r="B329" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>14692</v>
       </c>
@@ -12440,7 +12506,7 @@
       <c r="A330" t="s">
         <v>357</v>
       </c>
-      <c r="B330" s="10">
+      <c r="B330" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>6093</v>
       </c>
@@ -12461,7 +12527,7 @@
       <c r="A331" t="s">
         <v>358</v>
       </c>
-      <c r="B331" s="10">
+      <c r="B331" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>18562</v>
       </c>
@@ -12482,7 +12548,7 @@
       <c r="A332" t="s">
         <v>359</v>
       </c>
-      <c r="B332" s="10">
+      <c r="B332" s="5">
         <f t="shared" ca="1" si="19"/>
         <v>11155</v>
       </c>
@@ -12503,7 +12569,7 @@
       <c r="A333" t="s">
         <v>360</v>
       </c>
-      <c r="B333" s="10">
+      <c r="B333" s="5">
         <f t="shared" ref="B333:B396" ca="1" si="23">MOD(B332*F$11+F$12,F$13)</f>
         <v>2000</v>
       </c>
@@ -12524,7 +12590,7 @@
       <c r="A334" t="s">
         <v>361</v>
       </c>
-      <c r="B334" s="10">
+      <c r="B334" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>25545</v>
       </c>
@@ -12545,7 +12611,7 @@
       <c r="A335" t="s">
         <v>362</v>
       </c>
-      <c r="B335" s="10">
+      <c r="B335" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>27342</v>
       </c>
@@ -12566,7 +12632,7 @@
       <c r="A336" t="s">
         <v>363</v>
       </c>
-      <c r="B336" s="10">
+      <c r="B336" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>28143</v>
       </c>
@@ -12587,7 +12653,7 @@
       <c r="A337" t="s">
         <v>364</v>
       </c>
-      <c r="B337" s="10">
+      <c r="B337" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>20732</v>
       </c>
@@ -12608,7 +12674,7 @@
       <c r="A338" t="s">
         <v>365</v>
       </c>
-      <c r="B338" s="10">
+      <c r="B338" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>29573</v>
       </c>
@@ -12629,7 +12695,7 @@
       <c r="A339" t="s">
         <v>366</v>
       </c>
-      <c r="B339" s="10">
+      <c r="B339" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>26074</v>
       </c>
@@ -12650,7 +12716,7 @@
       <c r="A340" t="s">
         <v>367</v>
       </c>
-      <c r="B340" s="10">
+      <c r="B340" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>31243</v>
       </c>
@@ -12671,7 +12737,7 @@
       <c r="A341" t="s">
         <v>368</v>
       </c>
-      <c r="B341" s="10">
+      <c r="B341" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>232</v>
       </c>
@@ -12692,7 +12758,7 @@
       <c r="A342" t="s">
         <v>369</v>
       </c>
-      <c r="B342" s="10">
+      <c r="B342" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>17153</v>
       </c>
@@ -12713,7 +12779,7 @@
       <c r="A343" t="s">
         <v>370</v>
       </c>
-      <c r="B343" s="10">
+      <c r="B343" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>1446</v>
       </c>
@@ -12734,7 +12800,7 @@
       <c r="A344" t="s">
         <v>371</v>
       </c>
-      <c r="B344" s="10">
+      <c r="B344" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>11239</v>
       </c>
@@ -12755,7 +12821,7 @@
       <c r="A345" t="s">
         <v>372</v>
       </c>
-      <c r="B345" s="10">
+      <c r="B345" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>17300</v>
       </c>
@@ -12776,7 +12842,7 @@
       <c r="A346" t="s">
         <v>373</v>
       </c>
-      <c r="B346" s="10">
+      <c r="B346" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>3645</v>
       </c>
@@ -12797,7 +12863,7 @@
       <c r="A347" t="s">
         <v>374</v>
       </c>
-      <c r="B347" s="10">
+      <c r="B347" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>22066</v>
       </c>
@@ -12818,7 +12884,7 @@
       <c r="A348" t="s">
         <v>375</v>
       </c>
-      <c r="B348" s="10">
+      <c r="B348" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>8067</v>
       </c>
@@ -12839,7 +12905,7 @@
       <c r="A349" t="s">
         <v>376</v>
       </c>
-      <c r="B349" s="10">
+      <c r="B349" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>1280</v>
       </c>
@@ -12860,7 +12926,7 @@
       <c r="A350" t="s">
         <v>377</v>
       </c>
-      <c r="B350" s="10">
+      <c r="B350" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>20793</v>
       </c>
@@ -12881,7 +12947,7 @@
       <c r="A351" t="s">
         <v>378</v>
       </c>
-      <c r="B351" s="10">
+      <c r="B351" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>9086</v>
       </c>
@@ -12902,7 +12968,7 @@
       <c r="A352" t="s">
         <v>379</v>
       </c>
-      <c r="B352" s="10">
+      <c r="B352" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>12511</v>
       </c>
@@ -12923,7 +12989,7 @@
       <c r="A353" t="s">
         <v>380</v>
       </c>
-      <c r="B353" s="10">
+      <c r="B353" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>28972</v>
       </c>
@@ -12944,7 +13010,7 @@
       <c r="A354" t="s">
         <v>381</v>
       </c>
-      <c r="B354" s="10">
+      <c r="B354" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>18421</v>
       </c>
@@ -12965,7 +13031,7 @@
       <c r="A355" t="s">
         <v>382</v>
       </c>
-      <c r="B355" s="10">
+      <c r="B355" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>31114</v>
       </c>
@@ -12986,7 +13052,7 @@
       <c r="A356" t="s">
         <v>383</v>
       </c>
-      <c r="B356" s="10">
+      <c r="B356" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>31739</v>
       </c>
@@ -13007,7 +13073,7 @@
       <c r="A357" t="s">
         <v>384</v>
       </c>
-      <c r="B357" s="10">
+      <c r="B357" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>29720</v>
       </c>
@@ -13028,7 +13094,7 @@
       <c r="A358" t="s">
         <v>385</v>
       </c>
-      <c r="B358" s="10">
+      <c r="B358" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>28273</v>
       </c>
@@ -13049,7 +13115,7 @@
       <c r="A359" t="s">
         <v>386</v>
       </c>
-      <c r="B359" s="10">
+      <c r="B359" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>9302</v>
       </c>
@@ -13070,7 +13136,7 @@
       <c r="A360" t="s">
         <v>387</v>
       </c>
-      <c r="B360" s="10">
+      <c r="B360" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>23767</v>
       </c>
@@ -13091,7 +13157,7 @@
       <c r="A361" t="s">
         <v>388</v>
       </c>
-      <c r="B361" s="10">
+      <c r="B361" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>14788</v>
       </c>
@@ -13112,7 +13178,7 @@
       <c r="A362" t="s">
         <v>389</v>
       </c>
-      <c r="B362" s="10">
+      <c r="B362" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>173</v>
       </c>
@@ -13133,7 +13199,7 @@
       <c r="A363" t="s">
         <v>390</v>
       </c>
-      <c r="B363" s="10">
+      <c r="B363" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>12258</v>
       </c>
@@ -13154,7 +13220,7 @@
       <c r="A364" t="s">
         <v>391</v>
       </c>
-      <c r="B364" s="10">
+      <c r="B364" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>28531</v>
       </c>
@@ -13175,7 +13241,7 @@
       <c r="A365" t="s">
         <v>392</v>
       </c>
-      <c r="B365" s="10">
+      <c r="B365" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>11824</v>
       </c>
@@ -13196,7 +13262,7 @@
       <c r="A366" t="s">
         <v>393</v>
       </c>
-      <c r="B366" s="10">
+      <c r="B366" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>31401</v>
       </c>
@@ -13217,7 +13283,7 @@
       <c r="A367" t="s">
         <v>394</v>
       </c>
-      <c r="B367" s="10">
+      <c r="B367" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>26670</v>
       </c>
@@ -13238,7 +13304,7 @@
       <c r="A368" t="s">
         <v>395</v>
       </c>
-      <c r="B368" s="10">
+      <c r="B368" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>4047</v>
       </c>
@@ -13259,7 +13325,7 @@
       <c r="A369" t="s">
         <v>396</v>
       </c>
-      <c r="B369" s="10">
+      <c r="B369" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>32092</v>
       </c>
@@ -13280,7 +13346,7 @@
       <c r="A370" t="s">
         <v>397</v>
       </c>
-      <c r="B370" s="10">
+      <c r="B370" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>6245</v>
       </c>
@@ -13301,7 +13367,7 @@
       <c r="A371" t="s">
         <v>398</v>
       </c>
-      <c r="B371" s="10">
+      <c r="B371" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>22842</v>
       </c>
@@ -13322,7 +13388,7 @@
       <c r="A372" t="s">
         <v>399</v>
       </c>
-      <c r="B372" s="10">
+      <c r="B372" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>23019</v>
       </c>
@@ -13343,7 +13409,7 @@
       <c r="A373" t="s">
         <v>400</v>
       </c>
-      <c r="B373" s="10">
+      <c r="B373" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>4936</v>
       </c>
@@ -13364,7 +13430,7 @@
       <c r="A374" t="s">
         <v>401</v>
       </c>
-      <c r="B374" s="10">
+      <c r="B374" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>21985</v>
       </c>
@@ -13385,7 +13451,7 @@
       <c r="A375" t="s">
         <v>402</v>
       </c>
-      <c r="B375" s="10">
+      <c r="B375" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>20230</v>
       </c>
@@ -13406,7 +13472,7 @@
       <c r="A376" t="s">
         <v>403</v>
       </c>
-      <c r="B376" s="10">
+      <c r="B376" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>10695</v>
       </c>
@@ -13427,7 +13493,7 @@
       <c r="A377" t="s">
         <v>404</v>
       </c>
-      <c r="B377" s="10">
+      <c r="B377" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>7156</v>
       </c>
@@ -13448,7 +13514,7 @@
       <c r="A378" t="s">
         <v>405</v>
       </c>
-      <c r="B378" s="10">
+      <c r="B378" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>28445</v>
       </c>
@@ -13469,7 +13535,7 @@
       <c r="A379" t="s">
         <v>406</v>
       </c>
-      <c r="B379" s="10">
+      <c r="B379" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>21906</v>
       </c>
@@ -13490,7 +13556,7 @@
       <c r="A380" t="s">
         <v>407</v>
       </c>
-      <c r="B380" s="10">
+      <c r="B380" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>7011</v>
       </c>
@@ -13511,7 +13577,7 @@
       <c r="A381" t="s">
         <v>408</v>
       </c>
-      <c r="B381" s="10">
+      <c r="B381" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>864</v>
       </c>
@@ -13532,7 +13598,7 @@
       <c r="A382" t="s">
         <v>409</v>
       </c>
-      <c r="B382" s="10">
+      <c r="B382" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>24601</v>
       </c>
@@ -13553,7 +13619,7 @@
       <c r="A383" t="s">
         <v>410</v>
       </c>
-      <c r="B383" s="10">
+      <c r="B383" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>14558</v>
       </c>
@@ -13574,7 +13640,7 @@
       <c r="A384" t="s">
         <v>411</v>
       </c>
-      <c r="B384" s="10">
+      <c r="B384" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>2751</v>
       </c>
@@ -13595,7 +13661,7 @@
       <c r="A385" t="s">
         <v>412</v>
       </c>
-      <c r="B385" s="10">
+      <c r="B385" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>30092</v>
       </c>
@@ -13616,7 +13682,7 @@
       <c r="A386" t="s">
         <v>413</v>
       </c>
-      <c r="B386" s="10">
+      <c r="B386" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>25813</v>
       </c>
@@ -13637,7 +13703,7 @@
       <c r="A387" t="s">
         <v>414</v>
       </c>
-      <c r="B387" s="10">
+      <c r="B387" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>1258</v>
       </c>
@@ -13658,7 +13724,7 @@
       <c r="A388" t="s">
         <v>415</v>
       </c>
-      <c r="B388" s="10">
+      <c r="B388" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>5083</v>
       </c>
@@ -13679,7 +13745,7 @@
       <c r="A389" t="s">
         <v>416</v>
       </c>
-      <c r="B389" s="10">
+      <c r="B389" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>24184</v>
       </c>
@@ -13700,7 +13766,7 @@
       <c r="A390" t="s">
         <v>417</v>
       </c>
-      <c r="B390" s="10">
+      <c r="B390" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>31057</v>
       </c>
@@ -13721,7 +13787,7 @@
       <c r="A391" t="s">
         <v>418</v>
       </c>
-      <c r="B391" s="10">
+      <c r="B391" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>1462</v>
       </c>
@@ -13742,7 +13808,7 @@
       <c r="A392" t="s">
         <v>419</v>
       </c>
-      <c r="B392" s="10">
+      <c r="B392" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>4791</v>
       </c>
@@ -13763,7 +13829,7 @@
       <c r="A393" t="s">
         <v>420</v>
       </c>
-      <c r="B393" s="10">
+      <c r="B393" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>27172</v>
       </c>
@@ -13784,7 +13850,7 @@
       <c r="A394" t="s">
         <v>421</v>
       </c>
-      <c r="B394" s="10">
+      <c r="B394" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>22925</v>
       </c>
@@ -13805,7 +13871,7 @@
       <c r="A395" t="s">
         <v>422</v>
       </c>
-      <c r="B395" s="10">
+      <c r="B395" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>18242</v>
       </c>
@@ -13826,7 +13892,7 @@
       <c r="A396" t="s">
         <v>423</v>
       </c>
-      <c r="B396" s="10">
+      <c r="B396" s="5">
         <f t="shared" ca="1" si="23"/>
         <v>9043</v>
       </c>
@@ -13847,7 +13913,7 @@
       <c r="A397" t="s">
         <v>424</v>
       </c>
-      <c r="B397" s="10">
+      <c r="B397" s="5">
         <f t="shared" ref="B397:B460" ca="1" si="27">MOD(B396*F$11+F$12,F$13)</f>
         <v>1168</v>
       </c>
@@ -13868,7 +13934,7 @@
       <c r="A398" t="s">
         <v>425</v>
       </c>
-      <c r="B398" s="10">
+      <c r="B398" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>393</v>
       </c>
@@ -13889,7 +13955,7 @@
       <c r="A399" t="s">
         <v>426</v>
       </c>
-      <c r="B399" s="10">
+      <c r="B399" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>5518</v>
       </c>
@@ -13910,7 +13976,7 @@
       <c r="A400" t="s">
         <v>427</v>
       </c>
-      <c r="B400" s="10">
+      <c r="B400" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>8623</v>
       </c>
@@ -13931,7 +13997,7 @@
       <c r="A401" t="s">
         <v>428</v>
       </c>
-      <c r="B401" s="10">
+      <c r="B401" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>22972</v>
       </c>
@@ -13952,7 +14018,7 @@
       <c r="A402" t="s">
         <v>429</v>
       </c>
-      <c r="B402" s="10">
+      <c r="B402" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>11589</v>
       </c>
@@ -13973,7 +14039,7 @@
       <c r="A403" t="s">
         <v>430</v>
       </c>
-      <c r="B403" s="10">
+      <c r="B403" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>31898</v>
       </c>
@@ -13994,7 +14060,7 @@
       <c r="A404" t="s">
         <v>431</v>
       </c>
-      <c r="B404" s="10">
+      <c r="B404" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>10699</v>
       </c>
@@ -14015,7 +14081,7 @@
       <c r="A405" t="s">
         <v>432</v>
       </c>
-      <c r="B405" s="10">
+      <c r="B405" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>21928</v>
       </c>
@@ -14036,7 +14102,7 @@
       <c r="A406" t="s">
         <v>433</v>
       </c>
-      <c r="B406" s="10">
+      <c r="B406" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>22721</v>
       </c>
@@ -14057,7 +14123,7 @@
       <c r="A407" t="s">
         <v>434</v>
       </c>
-      <c r="B407" s="10">
+      <c r="B407" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>18534</v>
       </c>
@@ -14078,7 +14144,7 @@
       <c r="A408" t="s">
         <v>435</v>
       </c>
-      <c r="B408" s="10">
+      <c r="B408" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>6055</v>
       </c>
@@ -14099,7 +14165,7 @@
       <c r="A409" t="s">
         <v>436</v>
       </c>
-      <c r="B409" s="10">
+      <c r="B409" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>9300</v>
       </c>
@@ -14120,7 +14186,7 @@
       <c r="A410" t="s">
         <v>437</v>
       </c>
-      <c r="B410" s="10">
+      <c r="B410" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>16381</v>
       </c>
@@ -14141,7 +14207,7 @@
       <c r="A411" t="s">
         <v>438</v>
       </c>
-      <c r="B411" s="10">
+      <c r="B411" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>1266</v>
       </c>
@@ -14162,7 +14228,7 @@
       <c r="A412" t="s">
         <v>439</v>
       </c>
-      <c r="B412" s="10">
+      <c r="B412" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>1859</v>
       </c>
@@ -14183,7 +14249,7 @@
       <c r="A413" t="s">
         <v>440</v>
       </c>
-      <c r="B413" s="10">
+      <c r="B413" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>12736</v>
       </c>
@@ -14204,7 +14270,7 @@
       <c r="A414" t="s">
         <v>441</v>
       </c>
-      <c r="B414" s="10">
+      <c r="B414" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>24313</v>
       </c>
@@ -14225,7 +14291,7 @@
       <c r="A415" t="s">
         <v>442</v>
       </c>
-      <c r="B415" s="10">
+      <c r="B415" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>32318</v>
       </c>
@@ -14246,7 +14312,7 @@
       <c r="A416" t="s">
         <v>443</v>
       </c>
-      <c r="B416" s="10">
+      <c r="B416" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>21663</v>
       </c>
@@ -14267,7 +14333,7 @@
       <c r="A417" t="s">
         <v>444</v>
       </c>
-      <c r="B417" s="10">
+      <c r="B417" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>10732</v>
       </c>
@@ -14288,7 +14354,7 @@
       <c r="A418" t="s">
         <v>445</v>
       </c>
-      <c r="B418" s="10">
+      <c r="B418" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>29109</v>
       </c>
@@ -14309,7 +14375,7 @@
       <c r="A419" t="s">
         <v>446</v>
       </c>
-      <c r="B419" s="10">
+      <c r="B419" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>16458</v>
       </c>
@@ -14330,7 +14396,7 @@
       <c r="A420" t="s">
         <v>447</v>
       </c>
-      <c r="B420" s="10">
+      <c r="B420" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>7099</v>
       </c>
@@ -14351,7 +14417,7 @@
       <c r="A421" t="s">
         <v>448</v>
       </c>
-      <c r="B421" s="10">
+      <c r="B421" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>30936</v>
       </c>
@@ -14372,7 +14438,7 @@
       <c r="A422" t="s">
         <v>449</v>
       </c>
-      <c r="B422" s="10">
+      <c r="B422" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>29745</v>
       </c>
@@ -14393,7 +14459,7 @@
       <c r="A423" t="s">
         <v>450</v>
       </c>
-      <c r="B423" s="10">
+      <c r="B423" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>5910</v>
       </c>
@@ -14414,7 +14480,7 @@
       <c r="A424" t="s">
         <v>451</v>
       </c>
-      <c r="B424" s="10">
+      <c r="B424" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>14487</v>
       </c>
@@ -14435,7 +14501,7 @@
       <c r="A425" t="s">
         <v>452</v>
       </c>
-      <c r="B425" s="10">
+      <c r="B425" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>19076</v>
       </c>
@@ -14456,7 +14522,7 @@
       <c r="A426" t="s">
         <v>453</v>
       </c>
-      <c r="B426" s="10">
+      <c r="B426" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>8813</v>
       </c>
@@ -14477,7 +14543,7 @@
       <c r="A427" t="s">
         <v>454</v>
       </c>
-      <c r="B427" s="10">
+      <c r="B427" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>3746</v>
       </c>
@@ -14498,7 +14564,7 @@
       <c r="A428" t="s">
         <v>455</v>
       </c>
-      <c r="B428" s="10">
+      <c r="B428" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>18227</v>
       </c>
@@ -14519,7 +14585,7 @@
       <c r="A429" t="s">
         <v>456</v>
       </c>
-      <c r="B429" s="10">
+      <c r="B429" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>2800</v>
       </c>
@@ -14540,7 +14606,7 @@
       <c r="A430" t="s">
         <v>457</v>
       </c>
-      <c r="B430" s="10">
+      <c r="B430" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>30825</v>
       </c>
@@ -14561,7 +14627,7 @@
       <c r="A431" t="s">
         <v>458</v>
       </c>
-      <c r="B431" s="10">
+      <c r="B431" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>29422</v>
       </c>
@@ -14582,7 +14648,7 @@
       <c r="A432" t="s">
         <v>459</v>
       </c>
-      <c r="B432" s="10">
+      <c r="B432" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>9103</v>
       </c>
@@ -14603,7 +14669,7 @@
       <c r="A433" t="s">
         <v>460</v>
       </c>
-      <c r="B433" s="10">
+      <c r="B433" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>26140</v>
       </c>
@@ -14624,7 +14690,7 @@
       <c r="A434" t="s">
         <v>461</v>
       </c>
-      <c r="B434" s="10">
+      <c r="B434" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>12837</v>
       </c>
@@ -14645,7 +14711,7 @@
       <c r="A435" t="s">
         <v>462</v>
       </c>
-      <c r="B435" s="10">
+      <c r="B435" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>20474</v>
       </c>
@@ -14666,7 +14732,7 @@
       <c r="A436" t="s">
         <v>463</v>
       </c>
-      <c r="B436" s="10">
+      <c r="B436" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>27051</v>
       </c>
@@ -14687,7 +14753,7 @@
       <c r="A437" t="s">
         <v>464</v>
       </c>
-      <c r="B437" s="10">
+      <c r="B437" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>18440</v>
       </c>
@@ -14708,7 +14774,7 @@
       <c r="A438" t="s">
         <v>465</v>
       </c>
-      <c r="B438" s="10">
+      <c r="B438" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>19361</v>
       </c>
@@ -14729,7 +14795,7 @@
       <c r="A439" t="s">
         <v>466</v>
       </c>
-      <c r="B439" s="10">
+      <c r="B439" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>29126</v>
       </c>
@@ -14750,7 +14816,7 @@
       <c r="A440" t="s">
         <v>467</v>
       </c>
-      <c r="B440" s="10">
+      <c r="B440" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>30087</v>
       </c>
@@ -14771,7 +14837,7 @@
       <c r="A441" t="s">
         <v>468</v>
       </c>
-      <c r="B441" s="10">
+      <c r="B441" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>23732</v>
       </c>
@@ -14792,7 +14858,7 @@
       <c r="A442" t="s">
         <v>469</v>
       </c>
-      <c r="B442" s="10">
+      <c r="B442" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>221</v>
       </c>
@@ -14813,7 +14879,7 @@
       <c r="A443" t="s">
         <v>470</v>
       </c>
-      <c r="B443" s="10">
+      <c r="B443" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>25682</v>
       </c>
@@ -14834,7 +14900,7 @@
       <c r="A444" t="s">
         <v>471</v>
       </c>
-      <c r="B444" s="10">
+      <c r="B444" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>25379</v>
       </c>
@@ -14855,7 +14921,7 @@
       <c r="A445" t="s">
         <v>472</v>
       </c>
-      <c r="B445" s="10">
+      <c r="B445" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>4128</v>
       </c>
@@ -14876,7 +14942,7 @@
       <c r="A446" t="s">
         <v>473</v>
       </c>
-      <c r="B446" s="10">
+      <c r="B446" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>19929</v>
       </c>
@@ -14897,7 +14963,7 @@
       <c r="A447" t="s">
         <v>474</v>
       </c>
-      <c r="B447" s="10">
+      <c r="B447" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>29598</v>
       </c>
@@ -14918,7 +14984,7 @@
       <c r="A448" t="s">
         <v>475</v>
       </c>
-      <c r="B448" s="10">
+      <c r="B448" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>3711</v>
       </c>
@@ -14939,7 +15005,7 @@
       <c r="A449" t="s">
         <v>476</v>
       </c>
-      <c r="B449" s="10">
+      <c r="B449" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>3660</v>
       </c>
@@ -14960,7 +15026,7 @@
       <c r="A450" t="s">
         <v>477</v>
       </c>
-      <c r="B450" s="10">
+      <c r="B450" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>28309</v>
       </c>
@@ -14981,7 +15047,7 @@
       <c r="A451" t="s">
         <v>478</v>
       </c>
-      <c r="B451" s="10">
+      <c r="B451" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>11178</v>
       </c>
@@ -15002,7 +15068,7 @@
       <c r="A452" t="s">
         <v>479</v>
       </c>
-      <c r="B452" s="10">
+      <c r="B452" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>5019</v>
       </c>
@@ -15023,7 +15089,7 @@
       <c r="A453" t="s">
         <v>480</v>
       </c>
-      <c r="B453" s="10">
+      <c r="B453" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>17208</v>
       </c>
@@ -15044,7 +15110,7 @@
       <c r="A454" t="s">
         <v>481</v>
       </c>
-      <c r="B454" s="10">
+      <c r="B454" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>24337</v>
       </c>
@@ -15065,7 +15131,7 @@
       <c r="A455" t="s">
         <v>482</v>
       </c>
-      <c r="B455" s="10">
+      <c r="B455" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>22646</v>
       </c>
@@ -15086,7 +15152,7 @@
       <c r="A456" t="s">
         <v>483</v>
       </c>
-      <c r="B456" s="10">
+      <c r="B456" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>20087</v>
       </c>
@@ -15107,7 +15173,7 @@
       <c r="A457" t="s">
         <v>484</v>
       </c>
-      <c r="B457" s="10">
+      <c r="B457" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>23268</v>
       </c>
@@ -15128,7 +15194,7 @@
       <c r="A458" t="s">
         <v>485</v>
       </c>
-      <c r="B458" s="10">
+      <c r="B458" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>23373</v>
       </c>
@@ -15149,7 +15215,7 @@
       <c r="A459" t="s">
         <v>486</v>
       </c>
-      <c r="B459" s="10">
+      <c r="B459" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>1538</v>
       </c>
@@ -15170,7 +15236,7 @@
       <c r="A460" t="s">
         <v>487</v>
       </c>
-      <c r="B460" s="10">
+      <c r="B460" s="5">
         <f t="shared" ca="1" si="27"/>
         <v>23315</v>
       </c>
@@ -15191,7 +15257,7 @@
       <c r="A461" t="s">
         <v>488</v>
       </c>
-      <c r="B461" s="10">
+      <c r="B461" s="5">
         <f t="shared" ref="B461" ca="1" si="31">MOD(B460*F$11+F$12,F$13)</f>
         <v>16720</v>
       </c>
@@ -15230,613 +15296,613 @@
     <row r="2" spans="1:1">
       <c r="A2" s="3">
         <f ca="1">ROUND(NORMINV(RAND(),68,3.75),1)</f>
-        <v>71.2</v>
+        <v>73.099999999999994</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="3">
         <f t="shared" ref="A3:A66" ca="1" si="0">ROUND(NORMINV(RAND(),68,3.75),1)</f>
-        <v>65.400000000000006</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>70.599999999999994</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>70.7</v>
+        <v>70.3</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>62.2</v>
+        <v>70.3</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>72.5</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>68.3</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>70.3</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>61.3</v>
+        <v>69.3</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>56.8</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>68.5</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>66.900000000000006</v>
+        <v>71.900000000000006</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>74.400000000000006</v>
+        <v>64.099999999999994</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>66.8</v>
+        <v>68.3</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>73.5</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>67.5</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>73.400000000000006</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>68.900000000000006</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>64.099999999999994</v>
+        <v>67.8</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>64.599999999999994</v>
+        <v>71.099999999999994</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>61.8</v>
+        <v>65.900000000000006</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>66.099999999999994</v>
+        <v>65.3</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>73.8</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>61.7</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>68.5</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>66</v>
+        <v>65.900000000000006</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>65.5</v>
+        <v>67.099999999999994</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>73</v>
+        <v>65.3</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>70.599999999999994</v>
+        <v>67.8</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>72.599999999999994</v>
+        <v>68.900000000000006</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>67.900000000000006</v>
+        <v>72.8</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>63.8</v>
+        <v>68.7</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>65</v>
+        <v>69.900000000000006</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>68.8</v>
+        <v>60.9</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>68.400000000000006</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>67.099999999999994</v>
+        <v>68.7</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>74.099999999999994</v>
+        <v>76.7</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>68.099999999999994</v>
+        <v>68.7</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>70.599999999999994</v>
+        <v>70.2</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>75.400000000000006</v>
+        <v>69.900000000000006</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>68.099999999999994</v>
+        <v>68.7</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>67</v>
+        <v>72.900000000000006</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>72.7</v>
+        <v>63.1</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>67</v>
+        <v>65.400000000000006</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>65.2</v>
+        <v>63.2</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>64.3</v>
+        <v>62.1</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>64</v>
+        <v>73.099999999999994</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>72.400000000000006</v>
+        <v>62.9</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>76.3</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>72.5</v>
+        <v>67.400000000000006</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>70.099999999999994</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>70.8</v>
+        <v>68.099999999999994</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>66.3</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>68</v>
+        <v>67.8</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>65.5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>67.099999999999994</v>
+        <v>73.400000000000006</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>65.3</v>
+        <v>68.7</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>63.4</v>
+        <v>69.900000000000006</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>63.3</v>
+        <v>76</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>69.7</v>
+        <v>61</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>59.4</v>
+        <v>75.5</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>66.599999999999994</v>
+        <v>66.099999999999994</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>64.400000000000006</v>
+        <v>68.3</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>60.6</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>64.5</v>
+        <v>65</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="3">
         <f t="shared" ref="A67:A103" ca="1" si="1">ROUND(NORMINV(RAND(),68,3.75),1)</f>
-        <v>73.2</v>
+        <v>72.599999999999994</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>65.599999999999994</v>
+        <v>71.2</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>65.7</v>
+        <v>68.400000000000006</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>66.099999999999994</v>
+        <v>64.400000000000006</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>65.400000000000006</v>
+        <v>70.3</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>70.2</v>
+        <v>66.3</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>68.900000000000006</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>75.7</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>65.900000000000006</v>
+        <v>69.900000000000006</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>72.599999999999994</v>
+        <v>72.7</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>75.900000000000006</v>
+        <v>75.099999999999994</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>69.7</v>
+        <v>65.599999999999994</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>72.400000000000006</v>
+        <v>73.099999999999994</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>66.599999999999994</v>
+        <v>72.2</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>75</v>
+        <v>67.099999999999994</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>71.900000000000006</v>
+        <v>63.8</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>62.7</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>64.7</v>
+        <v>67.400000000000006</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>65.099999999999994</v>
+        <v>70.3</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>65</v>
+        <v>68.599999999999994</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>74.099999999999994</v>
+        <v>63.8</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>70.400000000000006</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>63.6</v>
+        <v>72.7</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>65.599999999999994</v>
+        <v>70.599999999999994</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>61.6</v>
+        <v>65.099999999999994</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>76.599999999999994</v>
+        <v>63.2</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>67</v>
+        <v>69.900000000000006</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>66.400000000000006</v>
+        <v>69</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>69.099999999999994</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>73.2</v>
+        <v>77</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>68.8</v>
+        <v>70.7</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>68.5</v>
+        <v>66.8</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>68.599999999999994</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>71.599999999999994</v>
+        <v>64.099999999999994</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>64.3</v>
+        <v>70.3</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>70.3</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>65.400000000000006</v>
+        <v>68.7</v>
       </c>
     </row>
   </sheetData>
@@ -15856,78 +15922,78 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:8">
-      <c r="B2" s="97" t="s">
+      <c r="B2" s="38" t="s">
         <v>490</v>
       </c>
-      <c r="C2" s="97"/>
-      <c r="D2" s="97"/>
-      <c r="E2" s="97"/>
-      <c r="F2" s="97"/>
-      <c r="G2" s="97"/>
-      <c r="H2" s="97"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
     </row>
     <row r="3" spans="2:8">
-      <c r="B3" s="97"/>
-      <c r="C3" s="97"/>
-      <c r="D3" s="97"/>
-      <c r="E3" s="97"/>
-      <c r="F3" s="97"/>
-      <c r="G3" s="97"/>
-      <c r="H3" s="97"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
     </row>
     <row r="4" spans="2:8">
-      <c r="B4" s="97"/>
-      <c r="C4" s="97"/>
-      <c r="D4" s="97"/>
-      <c r="E4" s="97"/>
-      <c r="F4" s="97"/>
-      <c r="G4" s="97"/>
-      <c r="H4" s="97"/>
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
     </row>
     <row r="5" spans="2:8">
-      <c r="B5" s="97"/>
-      <c r="C5" s="97"/>
-      <c r="D5" s="97"/>
-      <c r="E5" s="97"/>
-      <c r="F5" s="97"/>
-      <c r="G5" s="97"/>
-      <c r="H5" s="97"/>
+      <c r="B5" s="38"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="38"/>
     </row>
     <row r="6" spans="2:8">
-      <c r="B6" s="97"/>
-      <c r="C6" s="97"/>
-      <c r="D6" s="97"/>
-      <c r="E6" s="97"/>
-      <c r="F6" s="97"/>
-      <c r="G6" s="97"/>
-      <c r="H6" s="97"/>
+      <c r="B6" s="38"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="38"/>
+      <c r="E6" s="38"/>
+      <c r="F6" s="38"/>
+      <c r="G6" s="38"/>
+      <c r="H6" s="38"/>
     </row>
     <row r="7" spans="2:8">
-      <c r="B7" s="97"/>
-      <c r="C7" s="97"/>
-      <c r="D7" s="97"/>
-      <c r="E7" s="97"/>
-      <c r="F7" s="97"/>
-      <c r="G7" s="97"/>
-      <c r="H7" s="97"/>
+      <c r="B7" s="38"/>
+      <c r="C7" s="38"/>
+      <c r="D7" s="38"/>
+      <c r="E7" s="38"/>
+      <c r="F7" s="38"/>
+      <c r="G7" s="38"/>
+      <c r="H7" s="38"/>
     </row>
     <row r="8" spans="2:8">
-      <c r="B8" s="97"/>
-      <c r="C8" s="97"/>
-      <c r="D8" s="97"/>
-      <c r="E8" s="97"/>
-      <c r="F8" s="97"/>
-      <c r="G8" s="97"/>
-      <c r="H8" s="97"/>
+      <c r="B8" s="38"/>
+      <c r="C8" s="38"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="38"/>
     </row>
     <row r="9" spans="2:8">
-      <c r="B9" s="97"/>
-      <c r="C9" s="97"/>
-      <c r="D9" s="97"/>
-      <c r="E9" s="97"/>
-      <c r="F9" s="97"/>
-      <c r="G9" s="97"/>
-      <c r="H9" s="97"/>
+      <c r="B9" s="38"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="38"/>
+      <c r="G9" s="38"/>
+      <c r="H9" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -15949,17 +16015,8 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002C289946819CFF499E91D197BC975371" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="42fa38ab43a81509e346454549077e6d">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cca9fd2d-ef84-45c9-8063-8f4bd4c29606" xmlns:ns3="18557d39-01b8-4d71-9479-3fad465290ae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4c114411e421f950bcfed138b48f6b8f" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002C289946819CFF499E91D197BC975371" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="674b7a4e239a9748c7aaa97e309327a4">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cca9fd2d-ef84-45c9-8063-8f4bd4c29606" xmlns:ns3="18557d39-01b8-4d71-9479-3fad465290ae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="600253478e594d1349e02792803dc53a" ns2:_="" ns3:_="">
     <xsd:import namespace="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
     <xsd:import namespace="18557d39-01b8-4d71-9479-3fad465290ae"/>
     <xsd:element name="properties">
@@ -16174,6 +16231,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{924A8F3D-57F5-4941-A32A-55B7F7F7AF07}">
   <ds:schemaRefs>
@@ -16185,13 +16251,13 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F527DFD-99D6-4A6C-AC9B-EC23CCFE992B}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17F1EF20-95AB-4016-A693-6625F3A67214}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B648403-46AA-4E9E-9103-5722EF0AF416}"/>
 </file>